--- a/firebase_import_python/data_stok_beras_2026_06_juni.xlsx
+++ b/firebase_import_python/data_stok_beras_2026_06_juni.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Stok" sheetId="1" r:id="Rb104673176a844bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ringkasan" sheetId="2" r:id="R86095ca335d24d4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Stok" sheetId="1" r:id="R466c82d022074331"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ringkasan" sheetId="2" r:id="R55e97e1713684c90"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -55,7 +55,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="24">
+  <x:cellXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -104,6 +104,7 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -112,7 +113,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DataStok06" displayName="DataStok06" ref="A1:F255" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DataStok01" displayName="DataStok01" ref="A1:F258" headerRowCount="1">
   <x:tableColumns count="6">
     <x:tableColumn id="1" name="Tanggal"/>
     <x:tableColumn id="2" name="Merk/Jenis Beras"/>
@@ -310,7 +311,7 @@
         <x:v>BMW</x:v>
       </x:c>
       <x:c r="C2" s="17" t="n">
-        <x:v>38</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D2" s="17" t="n">
         <x:v>0</x:v>
@@ -330,7 +331,7 @@
         <x:v>Beras Walet</x:v>
       </x:c>
       <x:c r="C3" s="17" t="n">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D3" s="17" t="n">
         <x:v>0</x:v>
@@ -347,10 +348,10 @@
         <x:v>46174</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Karya Makmur</x:v>
+        <x:v>Pandan Wangi</x:v>
       </x:c>
       <x:c r="C4" s="17" t="n">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D4" s="17" t="n">
         <x:v>0</x:v>
@@ -367,10 +368,10 @@
         <x:v>46174</x:v>
       </x:c>
       <x:c r="B5" s="16" t="str">
-        <x:v>Keraton</x:v>
+        <x:v>Ramos</x:v>
       </x:c>
       <x:c r="C5" s="17" t="n">
-        <x:v>26</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D5" s="17" t="n">
         <x:v>0</x:v>
@@ -390,7 +391,7 @@
         <x:v>Ramos</x:v>
       </x:c>
       <x:c r="C6" s="17" t="n">
-        <x:v>37</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D6" s="17" t="n">
         <x:v>0</x:v>
@@ -399,7 +400,7 @@
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F6" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Tambahan stok masuk sesuai kebutuhan gudang, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -410,7 +411,7 @@
         <x:v>Rojo Lele</x:v>
       </x:c>
       <x:c r="C7" s="17" t="n">
-        <x:v>24</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D7" s="17" t="n">
         <x:v>0</x:v>
@@ -427,19 +428,19 @@
         <x:v>46174</x:v>
       </x:c>
       <x:c r="B8" s="16" t="str">
-        <x:v>BMW</x:v>
+        <x:v>Rojo Lele</x:v>
       </x:c>
       <x:c r="C8" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D8" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E8" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F8" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Tambahan stok masuk sesuai kebutuhan gudang, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -447,13 +448,13 @@
         <x:v>46174</x:v>
       </x:c>
       <x:c r="B9" s="16" t="str">
-        <x:v>Beras Walet</x:v>
+        <x:v>BMW</x:v>
       </x:c>
       <x:c r="C9" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E9" s="16" t="str">
         <x:v>Karung</x:v>
@@ -467,13 +468,13 @@
         <x:v>46174</x:v>
       </x:c>
       <x:c r="B10" s="16" t="str">
-        <x:v>Cap Kembang</x:v>
+        <x:v>Pandan Wangi</x:v>
       </x:c>
       <x:c r="C10" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D10" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E10" s="16" t="str">
         <x:v>Karung</x:v>
@@ -487,13 +488,13 @@
         <x:v>46174</x:v>
       </x:c>
       <x:c r="B11" s="16" t="str">
-        <x:v>Ir Cap Mercy</x:v>
+        <x:v>Ramos</x:v>
       </x:c>
       <x:c r="C11" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="17" t="n">
-        <x:v>27</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E11" s="16" t="str">
         <x:v>Karung</x:v>
@@ -507,13 +508,13 @@
         <x:v>46174</x:v>
       </x:c>
       <x:c r="B12" s="16" t="str">
-        <x:v>Pandan Wangi</x:v>
+        <x:v>Rojo Lele</x:v>
       </x:c>
       <x:c r="C12" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D12" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E12" s="16" t="str">
         <x:v>Karung</x:v>
@@ -524,16 +525,16 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="15" t="n">
-        <x:v>46174</x:v>
+        <x:v>46175</x:v>
       </x:c>
       <x:c r="B13" s="16" t="str">
-        <x:v>Rojo Lele</x:v>
+        <x:v>Beras Walet</x:v>
       </x:c>
       <x:c r="C13" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="17" t="n">
-        <x:v>23</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E13" s="16" t="str">
         <x:v>Karung</x:v>
@@ -547,13 +548,13 @@
         <x:v>46175</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>BMW</x:v>
+        <x:v>Ramos</x:v>
       </x:c>
       <x:c r="C14" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E14" s="16" t="str">
         <x:v>Karung</x:v>
@@ -567,13 +568,13 @@
         <x:v>46175</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>Beras Walet</x:v>
+        <x:v>Rojo Lele</x:v>
       </x:c>
       <x:c r="C15" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E15" s="16" t="str">
         <x:v>Karung</x:v>
@@ -584,82 +585,82 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="15" t="n">
-        <x:v>46175</x:v>
+        <x:v>46176</x:v>
       </x:c>
       <x:c r="B16" s="16" t="str">
-        <x:v>Cap Kembang</x:v>
+        <x:v>BMW</x:v>
       </x:c>
       <x:c r="C16" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D16" s="17" t="n">
-        <x:v>23</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E16" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F16" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="15" t="n">
-        <x:v>46175</x:v>
+        <x:v>46176</x:v>
       </x:c>
       <x:c r="B17" s="16" t="str">
-        <x:v>Karya Makmur</x:v>
+        <x:v>Beras Walet</x:v>
       </x:c>
       <x:c r="C17" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D17" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E17" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F17" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="15" t="n">
-        <x:v>46175</x:v>
+        <x:v>46176</x:v>
       </x:c>
       <x:c r="B18" s="16" t="str">
-        <x:v>Ramos</x:v>
+        <x:v>Cap Kembang</x:v>
       </x:c>
       <x:c r="C18" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D18" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E18" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F18" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="15" t="n">
-        <x:v>46175</x:v>
+        <x:v>46176</x:v>
       </x:c>
       <x:c r="B19" s="16" t="str">
-        <x:v>Rojo Lele</x:v>
+        <x:v>Ir Cap Mercy</x:v>
       </x:c>
       <x:c r="C19" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D19" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E19" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F19" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -667,10 +668,10 @@
         <x:v>46176</x:v>
       </x:c>
       <x:c r="B20" s="16" t="str">
-        <x:v>BMW</x:v>
+        <x:v>Pandan Wangi</x:v>
       </x:c>
       <x:c r="C20" s="17" t="n">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D20" s="17" t="n">
         <x:v>0</x:v>
@@ -687,10 +688,10 @@
         <x:v>46176</x:v>
       </x:c>
       <x:c r="B21" s="16" t="str">
-        <x:v>Cap Kembang</x:v>
+        <x:v>Sumber Raya</x:v>
       </x:c>
       <x:c r="C21" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D21" s="17" t="n">
         <x:v>0</x:v>
@@ -707,19 +708,19 @@
         <x:v>46176</x:v>
       </x:c>
       <x:c r="B22" s="16" t="str">
-        <x:v>Keraton</x:v>
+        <x:v>Beras Walet</x:v>
       </x:c>
       <x:c r="C22" s="17" t="n">
-        <x:v>37</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E22" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F22" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -727,19 +728,19 @@
         <x:v>46176</x:v>
       </x:c>
       <x:c r="B23" s="16" t="str">
-        <x:v>Pandan Wangi</x:v>
+        <x:v>Cap Kembang</x:v>
       </x:c>
       <x:c r="C23" s="17" t="n">
-        <x:v>37</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E23" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F23" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -750,16 +751,16 @@
         <x:v>Ramos</x:v>
       </x:c>
       <x:c r="C24" s="17" t="n">
-        <x:v>33</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E24" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F24" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -770,21 +771,21 @@
         <x:v>Rojo Lele</x:v>
       </x:c>
       <x:c r="C25" s="17" t="n">
-        <x:v>22</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E25" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F25" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="15" t="n">
-        <x:v>46176</x:v>
+        <x:v>46177</x:v>
       </x:c>
       <x:c r="B26" s="16" t="str">
         <x:v>Beras Walet</x:v>
@@ -793,7 +794,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E26" s="16" t="str">
         <x:v>Karung</x:v>
@@ -804,7 +805,7 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="15" t="n">
-        <x:v>46176</x:v>
+        <x:v>46177</x:v>
       </x:c>
       <x:c r="B27" s="16" t="str">
         <x:v>Ir Cap Mercy</x:v>
@@ -813,7 +814,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E27" s="16" t="str">
         <x:v>Karung</x:v>
@@ -824,16 +825,16 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="15" t="n">
-        <x:v>46176</x:v>
+        <x:v>46177</x:v>
       </x:c>
       <x:c r="B28" s="16" t="str">
-        <x:v>Karya Makmur</x:v>
+        <x:v>Pandan Wangi</x:v>
       </x:c>
       <x:c r="C28" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E28" s="16" t="str">
         <x:v>Karung</x:v>
@@ -844,16 +845,16 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="15" t="n">
-        <x:v>46176</x:v>
+        <x:v>46177</x:v>
       </x:c>
       <x:c r="B29" s="16" t="str">
-        <x:v>Keraton</x:v>
+        <x:v>Ramos</x:v>
       </x:c>
       <x:c r="C29" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E29" s="16" t="str">
         <x:v>Karung</x:v>
@@ -864,16 +865,16 @@
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="15" t="n">
-        <x:v>46176</x:v>
+        <x:v>46177</x:v>
       </x:c>
       <x:c r="B30" s="16" t="str">
-        <x:v>Ramos</x:v>
+        <x:v>Rojo Lele</x:v>
       </x:c>
       <x:c r="C30" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E30" s="16" t="str">
         <x:v>Karung</x:v>
@@ -884,136 +885,136 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="15" t="n">
-        <x:v>46176</x:v>
+        <x:v>46178</x:v>
       </x:c>
       <x:c r="B31" s="16" t="str">
-        <x:v>Rojo Lele</x:v>
+        <x:v>Beras Walet</x:v>
       </x:c>
       <x:c r="C31" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D31" s="17" t="n">
-        <x:v>22</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E31" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F31" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="15" t="n">
-        <x:v>46176</x:v>
+        <x:v>46178</x:v>
       </x:c>
       <x:c r="B32" s="16" t="str">
-        <x:v>Sumber Raya</x:v>
+        <x:v>Karya Makmur</x:v>
       </x:c>
       <x:c r="C32" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D32" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E32" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F32" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="15" t="n">
-        <x:v>46177</x:v>
+        <x:v>46178</x:v>
       </x:c>
       <x:c r="B33" s="16" t="str">
-        <x:v>Beras Walet</x:v>
+        <x:v>Keraton</x:v>
       </x:c>
       <x:c r="C33" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D33" s="17" t="n">
-        <x:v>26</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E33" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F33" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="15" t="n">
-        <x:v>46177</x:v>
+        <x:v>46178</x:v>
       </x:c>
       <x:c r="B34" s="16" t="str">
-        <x:v>Ir Cap Mercy</x:v>
+        <x:v>Pandan Wangi</x:v>
       </x:c>
       <x:c r="C34" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D34" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E34" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F34" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="15" t="n">
-        <x:v>46177</x:v>
+        <x:v>46178</x:v>
       </x:c>
       <x:c r="B35" s="16" t="str">
-        <x:v>Pandan Wangi</x:v>
+        <x:v>Ramos</x:v>
       </x:c>
       <x:c r="C35" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D35" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E35" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F35" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="15" t="n">
-        <x:v>46177</x:v>
+        <x:v>46178</x:v>
       </x:c>
       <x:c r="B36" s="16" t="str">
-        <x:v>Ramos</x:v>
+        <x:v>Rojo Lele</x:v>
       </x:c>
       <x:c r="C36" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D36" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E36" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F36" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="15" t="n">
-        <x:v>46177</x:v>
+        <x:v>46178</x:v>
       </x:c>
       <x:c r="B37" s="16" t="str">
-        <x:v>Rojo Lele</x:v>
+        <x:v>Cap Kembang</x:v>
       </x:c>
       <x:c r="C37" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="17" t="n">
-        <x:v>23</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E37" s="16" t="str">
         <x:v>Karung</x:v>
@@ -1024,16 +1025,16 @@
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="15" t="n">
-        <x:v>46177</x:v>
+        <x:v>46178</x:v>
       </x:c>
       <x:c r="B38" s="16" t="str">
-        <x:v>Sumber Raya</x:v>
+        <x:v>Karya Makmur</x:v>
       </x:c>
       <x:c r="C38" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E38" s="16" t="str">
         <x:v>Karung</x:v>
@@ -1047,13 +1048,13 @@
         <x:v>46178</x:v>
       </x:c>
       <x:c r="B39" s="16" t="str">
-        <x:v>Beras Walet</x:v>
+        <x:v>Pandan Wangi</x:v>
       </x:c>
       <x:c r="C39" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D39" s="17" t="n">
-        <x:v>26</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E39" s="16" t="str">
         <x:v>Karung</x:v>
@@ -1067,13 +1068,13 @@
         <x:v>46178</x:v>
       </x:c>
       <x:c r="B40" s="16" t="str">
-        <x:v>Cap Kembang</x:v>
+        <x:v>Ramos</x:v>
       </x:c>
       <x:c r="C40" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D40" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E40" s="16" t="str">
         <x:v>Karung</x:v>
@@ -1087,13 +1088,13 @@
         <x:v>46178</x:v>
       </x:c>
       <x:c r="B41" s="16" t="str">
-        <x:v>Karya Makmur</x:v>
+        <x:v>Rojo Lele</x:v>
       </x:c>
       <x:c r="C41" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D41" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E41" s="16" t="str">
         <x:v>Karung</x:v>
@@ -1107,13 +1108,13 @@
         <x:v>46178</x:v>
       </x:c>
       <x:c r="B42" s="16" t="str">
-        <x:v>Keraton</x:v>
+        <x:v>Sumber Raya</x:v>
       </x:c>
       <x:c r="C42" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D42" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E42" s="16" t="str">
         <x:v>Karung</x:v>
@@ -1124,10 +1125,10 @@
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="15" t="n">
-        <x:v>46178</x:v>
+        <x:v>46179</x:v>
       </x:c>
       <x:c r="B43" s="16" t="str">
-        <x:v>Ramos</x:v>
+        <x:v>Beras Walet</x:v>
       </x:c>
       <x:c r="C43" s="17" t="n">
         <x:v>0</x:v>
@@ -1144,16 +1145,16 @@
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="15" t="n">
-        <x:v>46178</x:v>
+        <x:v>46179</x:v>
       </x:c>
       <x:c r="B44" s="16" t="str">
-        <x:v>Rojo Lele</x:v>
+        <x:v>Ir Cap Mercy</x:v>
       </x:c>
       <x:c r="C44" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D44" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E44" s="16" t="str">
         <x:v>Karung</x:v>
@@ -1164,16 +1165,16 @@
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="15" t="n">
-        <x:v>46178</x:v>
+        <x:v>46179</x:v>
       </x:c>
       <x:c r="B45" s="16" t="str">
-        <x:v>Sumber Raya</x:v>
+        <x:v>Keraton</x:v>
       </x:c>
       <x:c r="C45" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D45" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E45" s="16" t="str">
         <x:v>Karung</x:v>
@@ -1187,19 +1188,19 @@
         <x:v>46179</x:v>
       </x:c>
       <x:c r="B46" s="16" t="str">
-        <x:v>Beras Walet</x:v>
+        <x:v>Ramos</x:v>
       </x:c>
       <x:c r="C46" s="17" t="n">
-        <x:v>33</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D46" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E46" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F46" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -1207,19 +1208,19 @@
         <x:v>46179</x:v>
       </x:c>
       <x:c r="B47" s="16" t="str">
-        <x:v>Ir Cap Mercy</x:v>
+        <x:v>Rojo Lele</x:v>
       </x:c>
       <x:c r="C47" s="17" t="n">
-        <x:v>29</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D47" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E47" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F47" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -1227,30 +1228,30 @@
         <x:v>46179</x:v>
       </x:c>
       <x:c r="B48" s="16" t="str">
-        <x:v>Ramos</x:v>
+        <x:v>Sumber Raya</x:v>
       </x:c>
       <x:c r="C48" s="17" t="n">
-        <x:v>32</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D48" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E48" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F48" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="15" t="n">
-        <x:v>46179</x:v>
+        <x:v>46180</x:v>
       </x:c>
       <x:c r="B49" s="16" t="str">
-        <x:v>Rojo Lele</x:v>
+        <x:v>Cap Kembang</x:v>
       </x:c>
       <x:c r="C49" s="17" t="n">
-        <x:v>36</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D49" s="17" t="n">
         <x:v>0</x:v>
@@ -1264,13 +1265,13 @@
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="15" t="n">
-        <x:v>46179</x:v>
+        <x:v>46180</x:v>
       </x:c>
       <x:c r="B50" s="16" t="str">
-        <x:v>Sumber Raya</x:v>
+        <x:v>Karya Makmur</x:v>
       </x:c>
       <x:c r="C50" s="17" t="n">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D50" s="17" t="n">
         <x:v>0</x:v>
@@ -1284,90 +1285,90 @@
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="15" t="n">
-        <x:v>46179</x:v>
+        <x:v>46180</x:v>
       </x:c>
       <x:c r="B51" s="16" t="str">
-        <x:v>Beras Walet</x:v>
+        <x:v>Keraton</x:v>
       </x:c>
       <x:c r="C51" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D51" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E51" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F51" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="15" t="n">
-        <x:v>46179</x:v>
+        <x:v>46180</x:v>
       </x:c>
       <x:c r="B52" s="16" t="str">
-        <x:v>Cap Kembang</x:v>
+        <x:v>Ramos</x:v>
       </x:c>
       <x:c r="C52" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D52" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E52" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F52" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="15" t="n">
-        <x:v>46179</x:v>
+        <x:v>46180</x:v>
       </x:c>
       <x:c r="B53" s="16" t="str">
-        <x:v>Karya Makmur</x:v>
+        <x:v>Rojo Lele</x:v>
       </x:c>
       <x:c r="C53" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D53" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E53" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F53" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="15" t="n">
-        <x:v>46179</x:v>
+        <x:v>46180</x:v>
       </x:c>
       <x:c r="B54" s="16" t="str">
-        <x:v>Pandan Wangi</x:v>
+        <x:v>Sumber Raya</x:v>
       </x:c>
       <x:c r="C54" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D54" s="17" t="n">
-        <x:v>40</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E54" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F54" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="15" t="n">
-        <x:v>46179</x:v>
+        <x:v>46180</x:v>
       </x:c>
       <x:c r="B55" s="16" t="str">
-        <x:v>Ramos</x:v>
+        <x:v>BMW</x:v>
       </x:c>
       <x:c r="C55" s="17" t="n">
         <x:v>0</x:v>
@@ -1384,16 +1385,16 @@
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="15" t="n">
-        <x:v>46179</x:v>
+        <x:v>46180</x:v>
       </x:c>
       <x:c r="B56" s="16" t="str">
-        <x:v>Rojo Lele</x:v>
+        <x:v>Beras Walet</x:v>
       </x:c>
       <x:c r="C56" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D56" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E56" s="16" t="str">
         <x:v>Karung</x:v>
@@ -1407,13 +1408,13 @@
         <x:v>46180</x:v>
       </x:c>
       <x:c r="B57" s="16" t="str">
-        <x:v>BMW</x:v>
+        <x:v>Cap Kembang</x:v>
       </x:c>
       <x:c r="C57" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D57" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E57" s="16" t="str">
         <x:v>Karung</x:v>
@@ -1427,13 +1428,13 @@
         <x:v>46180</x:v>
       </x:c>
       <x:c r="B58" s="16" t="str">
-        <x:v>Beras Walet</x:v>
+        <x:v>Ir Cap Mercy</x:v>
       </x:c>
       <x:c r="C58" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D58" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E58" s="16" t="str">
         <x:v>Karung</x:v>
@@ -1447,13 +1448,13 @@
         <x:v>46180</x:v>
       </x:c>
       <x:c r="B59" s="16" t="str">
-        <x:v>Ramos</x:v>
+        <x:v>Pandan Wangi</x:v>
       </x:c>
       <x:c r="C59" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D59" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E59" s="16" t="str">
         <x:v>Karung</x:v>
@@ -1473,7 +1474,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D60" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E60" s="16" t="str">
         <x:v>Karung</x:v>
@@ -1490,16 +1491,16 @@
         <x:v>Beras Walet</x:v>
       </x:c>
       <x:c r="C61" s="17" t="n">
-        <x:v>36</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D61" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E61" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F61" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -1510,16 +1511,16 @@
         <x:v>Karya Makmur</x:v>
       </x:c>
       <x:c r="C62" s="17" t="n">
-        <x:v>38</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D62" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E62" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F62" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -1527,19 +1528,19 @@
         <x:v>46181</x:v>
       </x:c>
       <x:c r="B63" s="16" t="str">
-        <x:v>Pandan Wangi</x:v>
+        <x:v>Keraton</x:v>
       </x:c>
       <x:c r="C63" s="17" t="n">
-        <x:v>26</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D63" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E63" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F63" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
@@ -1547,19 +1548,19 @@
         <x:v>46181</x:v>
       </x:c>
       <x:c r="B64" s="16" t="str">
-        <x:v>Ramos</x:v>
+        <x:v>Pandan Wangi</x:v>
       </x:c>
       <x:c r="C64" s="17" t="n">
-        <x:v>36</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D64" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E64" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F64" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
@@ -1567,19 +1568,19 @@
         <x:v>46181</x:v>
       </x:c>
       <x:c r="B65" s="16" t="str">
-        <x:v>Rojo Lele</x:v>
+        <x:v>Ramos</x:v>
       </x:c>
       <x:c r="C65" s="17" t="n">
-        <x:v>25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D65" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E65" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F65" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
@@ -1587,13 +1588,13 @@
         <x:v>46181</x:v>
       </x:c>
       <x:c r="B66" s="16" t="str">
-        <x:v>Beras Walet</x:v>
+        <x:v>Sumber Raya</x:v>
       </x:c>
       <x:c r="C66" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D66" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E66" s="16" t="str">
         <x:v>Karung</x:v>
@@ -1604,16 +1605,16 @@
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="15" t="n">
-        <x:v>46181</x:v>
+        <x:v>46182</x:v>
       </x:c>
       <x:c r="B67" s="16" t="str">
-        <x:v>Keraton</x:v>
+        <x:v>BMW</x:v>
       </x:c>
       <x:c r="C67" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D67" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E67" s="16" t="str">
         <x:v>Karung</x:v>
@@ -1624,16 +1625,16 @@
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="15" t="n">
-        <x:v>46181</x:v>
+        <x:v>46182</x:v>
       </x:c>
       <x:c r="B68" s="16" t="str">
-        <x:v>Ramos</x:v>
+        <x:v>Cap Kembang</x:v>
       </x:c>
       <x:c r="C68" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D68" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E68" s="16" t="str">
         <x:v>Karung</x:v>
@@ -1644,16 +1645,16 @@
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="15" t="n">
-        <x:v>46181</x:v>
+        <x:v>46182</x:v>
       </x:c>
       <x:c r="B69" s="16" t="str">
-        <x:v>Rojo Lele</x:v>
+        <x:v>Karya Makmur</x:v>
       </x:c>
       <x:c r="C69" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D69" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E69" s="16" t="str">
         <x:v>Karung</x:v>
@@ -1664,16 +1665,16 @@
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="15" t="n">
-        <x:v>46181</x:v>
+        <x:v>46182</x:v>
       </x:c>
       <x:c r="B70" s="16" t="str">
-        <x:v>Sumber Raya</x:v>
+        <x:v>Ramos</x:v>
       </x:c>
       <x:c r="C70" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D70" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E70" s="16" t="str">
         <x:v>Karung</x:v>
@@ -1687,13 +1688,13 @@
         <x:v>46182</x:v>
       </x:c>
       <x:c r="B71" s="16" t="str">
-        <x:v>BMW</x:v>
+        <x:v>Rojo Lele</x:v>
       </x:c>
       <x:c r="C71" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D71" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E71" s="16" t="str">
         <x:v>Karung</x:v>
@@ -1704,116 +1705,116 @@
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="15" t="n">
-        <x:v>46182</x:v>
+        <x:v>46183</x:v>
       </x:c>
       <x:c r="B72" s="16" t="str">
-        <x:v>Cap Kembang</x:v>
+        <x:v>Beras Walet</x:v>
       </x:c>
       <x:c r="C72" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D72" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E72" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F72" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="15" t="n">
-        <x:v>46182</x:v>
+        <x:v>46183</x:v>
       </x:c>
       <x:c r="B73" s="16" t="str">
-        <x:v>Karya Makmur</x:v>
+        <x:v>Cap Kembang</x:v>
       </x:c>
       <x:c r="C73" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D73" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E73" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F73" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="15" t="n">
-        <x:v>46182</x:v>
+        <x:v>46183</x:v>
       </x:c>
       <x:c r="B74" s="16" t="str">
-        <x:v>Keraton</x:v>
+        <x:v>Ir Cap Mercy</x:v>
       </x:c>
       <x:c r="C74" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D74" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E74" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F74" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="15" t="n">
-        <x:v>46182</x:v>
+        <x:v>46183</x:v>
       </x:c>
       <x:c r="B75" s="16" t="str">
-        <x:v>Pandan Wangi</x:v>
+        <x:v>Ramos</x:v>
       </x:c>
       <x:c r="C75" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D75" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E75" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F75" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="15" t="n">
-        <x:v>46182</x:v>
+        <x:v>46183</x:v>
       </x:c>
       <x:c r="B76" s="16" t="str">
-        <x:v>Ramos</x:v>
+        <x:v>Rojo Lele</x:v>
       </x:c>
       <x:c r="C76" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D76" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E76" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F76" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="15" t="n">
-        <x:v>46182</x:v>
+        <x:v>46183</x:v>
       </x:c>
       <x:c r="B77" s="16" t="str">
-        <x:v>Sumber Raya</x:v>
+        <x:v>BMW</x:v>
       </x:c>
       <x:c r="C77" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D77" s="17" t="n">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E77" s="16" t="str">
         <x:v>Karung</x:v>
@@ -1827,19 +1828,19 @@
         <x:v>46183</x:v>
       </x:c>
       <x:c r="B78" s="16" t="str">
-        <x:v>Beras Walet</x:v>
+        <x:v>Cap Kembang</x:v>
       </x:c>
       <x:c r="C78" s="17" t="n">
-        <x:v>25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D78" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E78" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F78" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
@@ -1847,19 +1848,19 @@
         <x:v>46183</x:v>
       </x:c>
       <x:c r="B79" s="16" t="str">
-        <x:v>Cap Kembang</x:v>
+        <x:v>Karya Makmur</x:v>
       </x:c>
       <x:c r="C79" s="17" t="n">
-        <x:v>32</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D79" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E79" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F79" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
@@ -1867,19 +1868,19 @@
         <x:v>46183</x:v>
       </x:c>
       <x:c r="B80" s="16" t="str">
-        <x:v>Keraton</x:v>
+        <x:v>Pandan Wangi</x:v>
       </x:c>
       <x:c r="C80" s="17" t="n">
-        <x:v>33</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D80" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E80" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F80" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
@@ -1890,16 +1891,16 @@
         <x:v>Ramos</x:v>
       </x:c>
       <x:c r="C81" s="17" t="n">
-        <x:v>38</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D81" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E81" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F81" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
@@ -1907,53 +1908,53 @@
         <x:v>46183</x:v>
       </x:c>
       <x:c r="B82" s="16" t="str">
-        <x:v>Rojo Lele</x:v>
+        <x:v>Sumber Raya</x:v>
       </x:c>
       <x:c r="C82" s="17" t="n">
-        <x:v>26</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D82" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E82" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F82" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="15" t="n">
-        <x:v>46183</x:v>
+        <x:v>46184</x:v>
       </x:c>
       <x:c r="B83" s="16" t="str">
-        <x:v>Sumber Raya</x:v>
+        <x:v>BMW</x:v>
       </x:c>
       <x:c r="C83" s="17" t="n">
-        <x:v>27</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D83" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E83" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F83" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="15" t="n">
-        <x:v>46183</x:v>
+        <x:v>46184</x:v>
       </x:c>
       <x:c r="B84" s="16" t="str">
-        <x:v>BMW</x:v>
+        <x:v>Beras Walet</x:v>
       </x:c>
       <x:c r="C84" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D84" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E84" s="16" t="str">
         <x:v>Karung</x:v>
@@ -1964,16 +1965,16 @@
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="15" t="n">
-        <x:v>46183</x:v>
+        <x:v>46184</x:v>
       </x:c>
       <x:c r="B85" s="16" t="str">
-        <x:v>Beras Walet</x:v>
+        <x:v>Keraton</x:v>
       </x:c>
       <x:c r="C85" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D85" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E85" s="16" t="str">
         <x:v>Karung</x:v>
@@ -1984,16 +1985,16 @@
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="15" t="n">
-        <x:v>46183</x:v>
+        <x:v>46184</x:v>
       </x:c>
       <x:c r="B86" s="16" t="str">
-        <x:v>Cap Kembang</x:v>
+        <x:v>Ramos</x:v>
       </x:c>
       <x:c r="C86" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D86" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E86" s="16" t="str">
         <x:v>Karung</x:v>
@@ -2004,136 +2005,136 @@
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="15" t="n">
-        <x:v>46183</x:v>
+        <x:v>46185</x:v>
       </x:c>
       <x:c r="B87" s="16" t="str">
-        <x:v>Pandan Wangi</x:v>
+        <x:v>BMW</x:v>
       </x:c>
       <x:c r="C87" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D87" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E87" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F87" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="15" t="n">
-        <x:v>46183</x:v>
+        <x:v>46185</x:v>
       </x:c>
       <x:c r="B88" s="16" t="str">
-        <x:v>Ramos</x:v>
+        <x:v>Beras Walet</x:v>
       </x:c>
       <x:c r="C88" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D88" s="17" t="n">
-        <x:v>24</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E88" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F88" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="15" t="n">
-        <x:v>46183</x:v>
+        <x:v>46185</x:v>
       </x:c>
       <x:c r="B89" s="16" t="str">
-        <x:v>Rojo Lele</x:v>
+        <x:v>Karya Makmur</x:v>
       </x:c>
       <x:c r="C89" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D89" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E89" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F89" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="15" t="n">
-        <x:v>46184</x:v>
+        <x:v>46185</x:v>
       </x:c>
       <x:c r="B90" s="16" t="str">
-        <x:v>Beras Walet</x:v>
+        <x:v>Pandan Wangi</x:v>
       </x:c>
       <x:c r="C90" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D90" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E90" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F90" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="15" t="n">
-        <x:v>46184</x:v>
+        <x:v>46185</x:v>
       </x:c>
       <x:c r="B91" s="16" t="str">
-        <x:v>Ir Cap Mercy</x:v>
+        <x:v>Ramos</x:v>
       </x:c>
       <x:c r="C91" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D91" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E91" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F91" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="15" t="n">
-        <x:v>46184</x:v>
+        <x:v>46185</x:v>
       </x:c>
       <x:c r="B92" s="16" t="str">
-        <x:v>Karya Makmur</x:v>
+        <x:v>Sumber Raya</x:v>
       </x:c>
       <x:c r="C92" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D92" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E92" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F92" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="15" t="n">
-        <x:v>46184</x:v>
+        <x:v>46185</x:v>
       </x:c>
       <x:c r="B93" s="16" t="str">
-        <x:v>Ramos</x:v>
+        <x:v>Cap Kembang</x:v>
       </x:c>
       <x:c r="C93" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D93" s="17" t="n">
-        <x:v>41</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E93" s="16" t="str">
         <x:v>Karung</x:v>
@@ -2144,16 +2145,16 @@
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="15" t="n">
-        <x:v>46184</x:v>
+        <x:v>46185</x:v>
       </x:c>
       <x:c r="B94" s="16" t="str">
-        <x:v>Rojo Lele</x:v>
+        <x:v>Ir Cap Mercy</x:v>
       </x:c>
       <x:c r="C94" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D94" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E94" s="16" t="str">
         <x:v>Karung</x:v>
@@ -2167,13 +2168,13 @@
         <x:v>46185</x:v>
       </x:c>
       <x:c r="B95" s="16" t="str">
-        <x:v>BMW</x:v>
+        <x:v>Karya Makmur</x:v>
       </x:c>
       <x:c r="C95" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D95" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E95" s="16" t="str">
         <x:v>Karung</x:v>
@@ -2187,13 +2188,13 @@
         <x:v>46185</x:v>
       </x:c>
       <x:c r="B96" s="16" t="str">
-        <x:v>Beras Walet</x:v>
+        <x:v>Keraton</x:v>
       </x:c>
       <x:c r="C96" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D96" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E96" s="16" t="str">
         <x:v>Karung</x:v>
@@ -2207,13 +2208,13 @@
         <x:v>46185</x:v>
       </x:c>
       <x:c r="B97" s="16" t="str">
-        <x:v>Cap Kembang</x:v>
+        <x:v>Ramos</x:v>
       </x:c>
       <x:c r="C97" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D97" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E97" s="16" t="str">
         <x:v>Karung</x:v>
@@ -2227,13 +2228,13 @@
         <x:v>46185</x:v>
       </x:c>
       <x:c r="B98" s="16" t="str">
-        <x:v>Karya Makmur</x:v>
+        <x:v>Rojo Lele</x:v>
       </x:c>
       <x:c r="C98" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D98" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E98" s="16" t="str">
         <x:v>Karung</x:v>
@@ -2247,13 +2248,13 @@
         <x:v>46185</x:v>
       </x:c>
       <x:c r="B99" s="16" t="str">
-        <x:v>Rojo Lele</x:v>
+        <x:v>Sumber Raya</x:v>
       </x:c>
       <x:c r="C99" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D99" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E99" s="16" t="str">
         <x:v>Karung</x:v>
@@ -2264,16 +2265,16 @@
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="15" t="n">
-        <x:v>46185</x:v>
+        <x:v>46186</x:v>
       </x:c>
       <x:c r="B100" s="16" t="str">
-        <x:v>Sumber Raya</x:v>
+        <x:v>BMW</x:v>
       </x:c>
       <x:c r="C100" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D100" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E100" s="16" t="str">
         <x:v>Karung</x:v>
@@ -2287,19 +2288,19 @@
         <x:v>46186</x:v>
       </x:c>
       <x:c r="B101" s="16" t="str">
-        <x:v>BMW</x:v>
+        <x:v>Beras Walet</x:v>
       </x:c>
       <x:c r="C101" s="17" t="n">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D101" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E101" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F101" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
@@ -2307,19 +2308,19 @@
         <x:v>46186</x:v>
       </x:c>
       <x:c r="B102" s="16" t="str">
-        <x:v>Beras Walet</x:v>
+        <x:v>Cap Kembang</x:v>
       </x:c>
       <x:c r="C102" s="17" t="n">
-        <x:v>23</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D102" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E102" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F102" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
@@ -2330,16 +2331,16 @@
         <x:v>Karya Makmur</x:v>
       </x:c>
       <x:c r="C103" s="17" t="n">
-        <x:v>30</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D103" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E103" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F103" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
@@ -2350,16 +2351,16 @@
         <x:v>Ramos</x:v>
       </x:c>
       <x:c r="C104" s="17" t="n">
-        <x:v>25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D104" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E104" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F104" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
@@ -2370,27 +2371,27 @@
         <x:v>Rojo Lele</x:v>
       </x:c>
       <x:c r="C105" s="17" t="n">
-        <x:v>34</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D105" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E105" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F105" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="15" t="n">
-        <x:v>46186</x:v>
+        <x:v>46187</x:v>
       </x:c>
       <x:c r="B106" s="16" t="str">
-        <x:v>Sumber Raya</x:v>
+        <x:v>BMW</x:v>
       </x:c>
       <x:c r="C106" s="17" t="n">
-        <x:v>30</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D106" s="17" t="n">
         <x:v>0</x:v>
@@ -2404,116 +2405,116 @@
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="15" t="n">
-        <x:v>46186</x:v>
+        <x:v>46187</x:v>
       </x:c>
       <x:c r="B107" s="16" t="str">
-        <x:v>Beras Walet</x:v>
+        <x:v>Karya Makmur</x:v>
       </x:c>
       <x:c r="C107" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D107" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E107" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F107" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="15" t="n">
-        <x:v>46186</x:v>
+        <x:v>46187</x:v>
       </x:c>
       <x:c r="B108" s="16" t="str">
         <x:v>Keraton</x:v>
       </x:c>
       <x:c r="C108" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D108" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E108" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F108" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="15" t="n">
-        <x:v>46186</x:v>
+        <x:v>46187</x:v>
       </x:c>
       <x:c r="B109" s="16" t="str">
-        <x:v>Pandan Wangi</x:v>
+        <x:v>Ramos</x:v>
       </x:c>
       <x:c r="C109" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D109" s="17" t="n">
-        <x:v>22</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E109" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F109" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="15" t="n">
-        <x:v>46186</x:v>
+        <x:v>46187</x:v>
       </x:c>
       <x:c r="B110" s="16" t="str">
-        <x:v>Ramos</x:v>
+        <x:v>Rojo Lele</x:v>
       </x:c>
       <x:c r="C110" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D110" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E110" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F110" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="15" t="n">
-        <x:v>46186</x:v>
+        <x:v>46187</x:v>
       </x:c>
       <x:c r="B111" s="16" t="str">
-        <x:v>Rojo Lele</x:v>
+        <x:v>Sumber Raya</x:v>
       </x:c>
       <x:c r="C111" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D111" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E111" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F111" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="15" t="n">
-        <x:v>46186</x:v>
+        <x:v>46187</x:v>
       </x:c>
       <x:c r="B112" s="16" t="str">
-        <x:v>Sumber Raya</x:v>
+        <x:v>Beras Walet</x:v>
       </x:c>
       <x:c r="C112" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D112" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E112" s="16" t="str">
         <x:v>Karung</x:v>
@@ -2527,13 +2528,13 @@
         <x:v>46187</x:v>
       </x:c>
       <x:c r="B113" s="16" t="str">
-        <x:v>Cap Kembang</x:v>
+        <x:v>Ir Cap Mercy</x:v>
       </x:c>
       <x:c r="C113" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D113" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E113" s="16" t="str">
         <x:v>Karung</x:v>
@@ -2547,13 +2548,13 @@
         <x:v>46187</x:v>
       </x:c>
       <x:c r="B114" s="16" t="str">
-        <x:v>Ir Cap Mercy</x:v>
+        <x:v>Keraton</x:v>
       </x:c>
       <x:c r="C114" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D114" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E114" s="16" t="str">
         <x:v>Karung</x:v>
@@ -2567,13 +2568,13 @@
         <x:v>46187</x:v>
       </x:c>
       <x:c r="B115" s="16" t="str">
-        <x:v>Keraton</x:v>
+        <x:v>Ramos</x:v>
       </x:c>
       <x:c r="C115" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D115" s="17" t="n">
-        <x:v>21</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E115" s="16" t="str">
         <x:v>Karung</x:v>
@@ -2587,13 +2588,13 @@
         <x:v>46187</x:v>
       </x:c>
       <x:c r="B116" s="16" t="str">
-        <x:v>Ramos</x:v>
+        <x:v>Rojo Lele</x:v>
       </x:c>
       <x:c r="C116" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D116" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E116" s="16" t="str">
         <x:v>Karung</x:v>
@@ -2604,22 +2605,22 @@
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="15" t="n">
-        <x:v>46188</x:v>
+        <x:v>46187</x:v>
       </x:c>
       <x:c r="B117" s="16" t="str">
-        <x:v>Beras Walet</x:v>
+        <x:v>Sumber Raya</x:v>
       </x:c>
       <x:c r="C117" s="17" t="n">
-        <x:v>25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D117" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E117" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F117" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="118">
@@ -2627,19 +2628,19 @@
         <x:v>46188</x:v>
       </x:c>
       <x:c r="B118" s="16" t="str">
-        <x:v>Cap Kembang</x:v>
+        <x:v>Beras Walet</x:v>
       </x:c>
       <x:c r="C118" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D118" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E118" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F118" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="119">
@@ -2647,19 +2648,19 @@
         <x:v>46188</x:v>
       </x:c>
       <x:c r="B119" s="16" t="str">
-        <x:v>Ir Cap Mercy</x:v>
+        <x:v>Rojo Lele</x:v>
       </x:c>
       <x:c r="C119" s="17" t="n">
-        <x:v>29</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D119" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E119" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F119" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="120">
@@ -2667,93 +2668,93 @@
         <x:v>46188</x:v>
       </x:c>
       <x:c r="B120" s="16" t="str">
-        <x:v>Pandan Wangi</x:v>
+        <x:v>Sumber Raya</x:v>
       </x:c>
       <x:c r="C120" s="17" t="n">
-        <x:v>36</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D120" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E120" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F120" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="15" t="n">
-        <x:v>46188</x:v>
+        <x:v>46189</x:v>
       </x:c>
       <x:c r="B121" s="16" t="str">
-        <x:v>Ramos</x:v>
+        <x:v>BMW</x:v>
       </x:c>
       <x:c r="C121" s="17" t="n">
-        <x:v>22</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D121" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E121" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F121" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="122">
       <x:c r="A122" s="15" t="n">
-        <x:v>46188</x:v>
+        <x:v>46189</x:v>
       </x:c>
       <x:c r="B122" s="16" t="str">
-        <x:v>Rojo Lele</x:v>
+        <x:v>Beras Walet</x:v>
       </x:c>
       <x:c r="C122" s="17" t="n">
-        <x:v>33</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D122" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E122" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F122" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="123">
       <x:c r="A123" s="15" t="n">
-        <x:v>46188</x:v>
+        <x:v>46189</x:v>
       </x:c>
       <x:c r="B123" s="16" t="str">
-        <x:v>Sumber Raya</x:v>
+        <x:v>Cap Kembang</x:v>
       </x:c>
       <x:c r="C123" s="17" t="n">
-        <x:v>29</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D123" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E123" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F123" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="15" t="n">
-        <x:v>46188</x:v>
+        <x:v>46189</x:v>
       </x:c>
       <x:c r="B124" s="16" t="str">
-        <x:v>BMW</x:v>
+        <x:v>Ir Cap Mercy</x:v>
       </x:c>
       <x:c r="C124" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D124" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E124" s="16" t="str">
         <x:v>Karung</x:v>
@@ -2764,16 +2765,16 @@
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="15" t="n">
-        <x:v>46188</x:v>
+        <x:v>46189</x:v>
       </x:c>
       <x:c r="B125" s="16" t="str">
-        <x:v>Beras Walet</x:v>
+        <x:v>Karya Makmur</x:v>
       </x:c>
       <x:c r="C125" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D125" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E125" s="16" t="str">
         <x:v>Karung</x:v>
@@ -2784,16 +2785,16 @@
     </x:row>
     <x:row r="126">
       <x:c r="A126" s="15" t="n">
-        <x:v>46188</x:v>
+        <x:v>46189</x:v>
       </x:c>
       <x:c r="B126" s="16" t="str">
-        <x:v>Ir Cap Mercy</x:v>
+        <x:v>Ramos</x:v>
       </x:c>
       <x:c r="C126" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D126" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E126" s="16" t="str">
         <x:v>Karung</x:v>
@@ -2804,16 +2805,16 @@
     </x:row>
     <x:row r="127">
       <x:c r="A127" s="15" t="n">
-        <x:v>46188</x:v>
+        <x:v>46189</x:v>
       </x:c>
       <x:c r="B127" s="16" t="str">
-        <x:v>Karya Makmur</x:v>
+        <x:v>Rojo Lele</x:v>
       </x:c>
       <x:c r="C127" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D127" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E127" s="16" t="str">
         <x:v>Karung</x:v>
@@ -2824,116 +2825,116 @@
     </x:row>
     <x:row r="128">
       <x:c r="A128" s="15" t="n">
-        <x:v>46188</x:v>
+        <x:v>46190</x:v>
       </x:c>
       <x:c r="B128" s="16" t="str">
-        <x:v>Keraton</x:v>
+        <x:v>Beras Walet</x:v>
       </x:c>
       <x:c r="C128" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D128" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E128" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F128" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="129">
       <x:c r="A129" s="15" t="n">
-        <x:v>46188</x:v>
+        <x:v>46190</x:v>
       </x:c>
       <x:c r="B129" s="16" t="str">
-        <x:v>Ramos</x:v>
+        <x:v>Ir Cap Mercy</x:v>
       </x:c>
       <x:c r="C129" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D129" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E129" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F129" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="130">
       <x:c r="A130" s="15" t="n">
-        <x:v>46188</x:v>
+        <x:v>46190</x:v>
       </x:c>
       <x:c r="B130" s="16" t="str">
-        <x:v>Rojo Lele</x:v>
+        <x:v>Ramos</x:v>
       </x:c>
       <x:c r="C130" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D130" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E130" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F130" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="131">
       <x:c r="A131" s="15" t="n">
-        <x:v>46188</x:v>
+        <x:v>46190</x:v>
       </x:c>
       <x:c r="B131" s="16" t="str">
-        <x:v>Sumber Raya</x:v>
+        <x:v>Rojo Lele</x:v>
       </x:c>
       <x:c r="C131" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D131" s="17" t="n">
-        <x:v>19</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E131" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F131" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="15" t="n">
-        <x:v>46189</x:v>
+        <x:v>46190</x:v>
       </x:c>
       <x:c r="B132" s="16" t="str">
-        <x:v>BMW</x:v>
+        <x:v>Sumber Raya</x:v>
       </x:c>
       <x:c r="C132" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D132" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E132" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F132" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="133">
       <x:c r="A133" s="15" t="n">
-        <x:v>46189</x:v>
+        <x:v>46190</x:v>
       </x:c>
       <x:c r="B133" s="16" t="str">
-        <x:v>Cap Kembang</x:v>
+        <x:v>BMW</x:v>
       </x:c>
       <x:c r="C133" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D133" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E133" s="16" t="str">
         <x:v>Karung</x:v>
@@ -2944,7 +2945,7 @@
     </x:row>
     <x:row r="134">
       <x:c r="A134" s="15" t="n">
-        <x:v>46189</x:v>
+        <x:v>46190</x:v>
       </x:c>
       <x:c r="B134" s="16" t="str">
         <x:v>Karya Makmur</x:v>
@@ -2953,7 +2954,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D134" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E134" s="16" t="str">
         <x:v>Karung</x:v>
@@ -2964,7 +2965,7 @@
     </x:row>
     <x:row r="135">
       <x:c r="A135" s="15" t="n">
-        <x:v>46189</x:v>
+        <x:v>46190</x:v>
       </x:c>
       <x:c r="B135" s="16" t="str">
         <x:v>Keraton</x:v>
@@ -2973,7 +2974,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D135" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E135" s="16" t="str">
         <x:v>Karung</x:v>
@@ -2984,7 +2985,7 @@
     </x:row>
     <x:row r="136">
       <x:c r="A136" s="15" t="n">
-        <x:v>46189</x:v>
+        <x:v>46190</x:v>
       </x:c>
       <x:c r="B136" s="16" t="str">
         <x:v>Pandan Wangi</x:v>
@@ -2993,7 +2994,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D136" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E136" s="16" t="str">
         <x:v>Karung</x:v>
@@ -3004,7 +3005,7 @@
     </x:row>
     <x:row r="137">
       <x:c r="A137" s="15" t="n">
-        <x:v>46189</x:v>
+        <x:v>46190</x:v>
       </x:c>
       <x:c r="B137" s="16" t="str">
         <x:v>Ramos</x:v>
@@ -3013,7 +3014,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D137" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E137" s="16" t="str">
         <x:v>Karung</x:v>
@@ -3024,7 +3025,7 @@
     </x:row>
     <x:row r="138">
       <x:c r="A138" s="15" t="n">
-        <x:v>46189</x:v>
+        <x:v>46190</x:v>
       </x:c>
       <x:c r="B138" s="16" t="str">
         <x:v>Sumber Raya</x:v>
@@ -3033,7 +3034,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D138" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E138" s="16" t="str">
         <x:v>Karung</x:v>
@@ -3044,93 +3045,93 @@
     </x:row>
     <x:row r="139">
       <x:c r="A139" s="15" t="n">
-        <x:v>46190</x:v>
+        <x:v>46191</x:v>
       </x:c>
       <x:c r="B139" s="16" t="str">
-        <x:v>BMW</x:v>
+        <x:v>Beras Walet</x:v>
       </x:c>
       <x:c r="C139" s="17" t="n">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D139" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E139" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F139" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="140">
       <x:c r="A140" s="15" t="n">
-        <x:v>46190</x:v>
+        <x:v>46191</x:v>
       </x:c>
       <x:c r="B140" s="16" t="str">
-        <x:v>Beras Walet</x:v>
+        <x:v>Ir Cap Mercy</x:v>
       </x:c>
       <x:c r="C140" s="17" t="n">
-        <x:v>30</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D140" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E140" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F140" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="141">
       <x:c r="A141" s="15" t="n">
-        <x:v>46190</x:v>
+        <x:v>46191</x:v>
       </x:c>
       <x:c r="B141" s="16" t="str">
-        <x:v>Keraton</x:v>
+        <x:v>Pandan Wangi</x:v>
       </x:c>
       <x:c r="C141" s="17" t="n">
-        <x:v>34</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D141" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E141" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F141" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="142">
       <x:c r="A142" s="15" t="n">
-        <x:v>46190</x:v>
+        <x:v>46191</x:v>
       </x:c>
       <x:c r="B142" s="16" t="str">
         <x:v>Ramos</x:v>
       </x:c>
       <x:c r="C142" s="17" t="n">
-        <x:v>29</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D142" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E142" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F142" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="143">
       <x:c r="A143" s="15" t="n">
-        <x:v>46190</x:v>
+        <x:v>46192</x:v>
       </x:c>
       <x:c r="B143" s="16" t="str">
-        <x:v>Rojo Lele</x:v>
+        <x:v>Beras Walet</x:v>
       </x:c>
       <x:c r="C143" s="17" t="n">
-        <x:v>23</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D143" s="17" t="n">
         <x:v>0</x:v>
@@ -3144,13 +3145,13 @@
     </x:row>
     <x:row r="144">
       <x:c r="A144" s="15" t="n">
-        <x:v>46190</x:v>
+        <x:v>46192</x:v>
       </x:c>
       <x:c r="B144" s="16" t="str">
-        <x:v>Sumber Raya</x:v>
+        <x:v>Cap Kembang</x:v>
       </x:c>
       <x:c r="C144" s="17" t="n">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D144" s="17" t="n">
         <x:v>0</x:v>
@@ -3164,76 +3165,76 @@
     </x:row>
     <x:row r="145">
       <x:c r="A145" s="15" t="n">
-        <x:v>46190</x:v>
+        <x:v>46192</x:v>
       </x:c>
       <x:c r="B145" s="16" t="str">
-        <x:v>Beras Walet</x:v>
+        <x:v>Karya Makmur</x:v>
       </x:c>
       <x:c r="C145" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D145" s="17" t="n">
-        <x:v>25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E145" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F145" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="146">
       <x:c r="A146" s="15" t="n">
-        <x:v>46190</x:v>
+        <x:v>46192</x:v>
       </x:c>
       <x:c r="B146" s="16" t="str">
-        <x:v>Ir Cap Mercy</x:v>
+        <x:v>Ramos</x:v>
       </x:c>
       <x:c r="C146" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D146" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E146" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F146" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="147">
       <x:c r="A147" s="15" t="n">
-        <x:v>46190</x:v>
+        <x:v>46192</x:v>
       </x:c>
       <x:c r="B147" s="16" t="str">
-        <x:v>Pandan Wangi</x:v>
+        <x:v>Rojo Lele</x:v>
       </x:c>
       <x:c r="C147" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D147" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E147" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F147" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="148">
       <x:c r="A148" s="15" t="n">
-        <x:v>46190</x:v>
+        <x:v>46192</x:v>
       </x:c>
       <x:c r="B148" s="16" t="str">
-        <x:v>Ramos</x:v>
+        <x:v>BMW</x:v>
       </x:c>
       <x:c r="C148" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D148" s="17" t="n">
-        <x:v>18</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E148" s="16" t="str">
         <x:v>Karung</x:v>
@@ -3244,16 +3245,16 @@
     </x:row>
     <x:row r="149">
       <x:c r="A149" s="15" t="n">
-        <x:v>46191</x:v>
+        <x:v>46192</x:v>
       </x:c>
       <x:c r="B149" s="16" t="str">
-        <x:v>BMW</x:v>
+        <x:v>Beras Walet</x:v>
       </x:c>
       <x:c r="C149" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D149" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E149" s="16" t="str">
         <x:v>Karung</x:v>
@@ -3264,16 +3265,16 @@
     </x:row>
     <x:row r="150">
       <x:c r="A150" s="15" t="n">
-        <x:v>46191</x:v>
+        <x:v>46192</x:v>
       </x:c>
       <x:c r="B150" s="16" t="str">
-        <x:v>Beras Walet</x:v>
+        <x:v>Cap Kembang</x:v>
       </x:c>
       <x:c r="C150" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D150" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E150" s="16" t="str">
         <x:v>Karung</x:v>
@@ -3284,16 +3285,16 @@
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="15" t="n">
-        <x:v>46191</x:v>
+        <x:v>46192</x:v>
       </x:c>
       <x:c r="B151" s="16" t="str">
-        <x:v>Cap Kembang</x:v>
+        <x:v>Ir Cap Mercy</x:v>
       </x:c>
       <x:c r="C151" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D151" s="17" t="n">
-        <x:v>23</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E151" s="16" t="str">
         <x:v>Karung</x:v>
@@ -3304,16 +3305,16 @@
     </x:row>
     <x:row r="152">
       <x:c r="A152" s="15" t="n">
-        <x:v>46191</x:v>
+        <x:v>46192</x:v>
       </x:c>
       <x:c r="B152" s="16" t="str">
-        <x:v>Ir Cap Mercy</x:v>
+        <x:v>Pandan Wangi</x:v>
       </x:c>
       <x:c r="C152" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D152" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E152" s="16" t="str">
         <x:v>Karung</x:v>
@@ -3324,16 +3325,16 @@
     </x:row>
     <x:row r="153">
       <x:c r="A153" s="15" t="n">
-        <x:v>46191</x:v>
+        <x:v>46192</x:v>
       </x:c>
       <x:c r="B153" s="16" t="str">
-        <x:v>Karya Makmur</x:v>
+        <x:v>Ramos</x:v>
       </x:c>
       <x:c r="C153" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D153" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E153" s="16" t="str">
         <x:v>Karung</x:v>
@@ -3344,16 +3345,16 @@
     </x:row>
     <x:row r="154">
       <x:c r="A154" s="15" t="n">
-        <x:v>46191</x:v>
+        <x:v>46193</x:v>
       </x:c>
       <x:c r="B154" s="16" t="str">
-        <x:v>Keraton</x:v>
+        <x:v>BMW</x:v>
       </x:c>
       <x:c r="C154" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D154" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E154" s="16" t="str">
         <x:v>Karung</x:v>
@@ -3364,16 +3365,16 @@
     </x:row>
     <x:row r="155">
       <x:c r="A155" s="15" t="n">
-        <x:v>46191</x:v>
+        <x:v>46193</x:v>
       </x:c>
       <x:c r="B155" s="16" t="str">
-        <x:v>Ramos</x:v>
+        <x:v>Beras Walet</x:v>
       </x:c>
       <x:c r="C155" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D155" s="17" t="n">
-        <x:v>26</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E155" s="16" t="str">
         <x:v>Karung</x:v>
@@ -3384,16 +3385,16 @@
     </x:row>
     <x:row r="156">
       <x:c r="A156" s="15" t="n">
-        <x:v>46192</x:v>
+        <x:v>46193</x:v>
       </x:c>
       <x:c r="B156" s="16" t="str">
-        <x:v>BMW</x:v>
+        <x:v>Karya Makmur</x:v>
       </x:c>
       <x:c r="C156" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D156" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E156" s="16" t="str">
         <x:v>Karung</x:v>
@@ -3404,16 +3405,16 @@
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="15" t="n">
-        <x:v>46192</x:v>
+        <x:v>46193</x:v>
       </x:c>
       <x:c r="B157" s="16" t="str">
-        <x:v>Beras Walet</x:v>
+        <x:v>Pandan Wangi</x:v>
       </x:c>
       <x:c r="C157" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D157" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E157" s="16" t="str">
         <x:v>Karung</x:v>
@@ -3424,16 +3425,16 @@
     </x:row>
     <x:row r="158">
       <x:c r="A158" s="15" t="n">
-        <x:v>46192</x:v>
+        <x:v>46193</x:v>
       </x:c>
       <x:c r="B158" s="16" t="str">
-        <x:v>Cap Kembang</x:v>
+        <x:v>Ramos</x:v>
       </x:c>
       <x:c r="C158" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D158" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E158" s="16" t="str">
         <x:v>Karung</x:v>
@@ -3444,16 +3445,16 @@
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="15" t="n">
-        <x:v>46192</x:v>
+        <x:v>46193</x:v>
       </x:c>
       <x:c r="B159" s="16" t="str">
-        <x:v>Ir Cap Mercy</x:v>
+        <x:v>Rojo Lele</x:v>
       </x:c>
       <x:c r="C159" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D159" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E159" s="16" t="str">
         <x:v>Karung</x:v>
@@ -3464,93 +3465,93 @@
     </x:row>
     <x:row r="160">
       <x:c r="A160" s="15" t="n">
-        <x:v>46192</x:v>
+        <x:v>46194</x:v>
       </x:c>
       <x:c r="B160" s="16" t="str">
-        <x:v>Karya Makmur</x:v>
+        <x:v>BMW</x:v>
       </x:c>
       <x:c r="C160" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D160" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E160" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F160" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="161">
       <x:c r="A161" s="15" t="n">
-        <x:v>46192</x:v>
+        <x:v>46194</x:v>
       </x:c>
       <x:c r="B161" s="16" t="str">
-        <x:v>Keraton</x:v>
+        <x:v>Ir Cap Mercy</x:v>
       </x:c>
       <x:c r="C161" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D161" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E161" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F161" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="162">
       <x:c r="A162" s="15" t="n">
-        <x:v>46192</x:v>
+        <x:v>46194</x:v>
       </x:c>
       <x:c r="B162" s="16" t="str">
-        <x:v>Rojo Lele</x:v>
+        <x:v>Karya Makmur</x:v>
       </x:c>
       <x:c r="C162" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D162" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E162" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F162" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="163">
       <x:c r="A163" s="15" t="n">
-        <x:v>46192</x:v>
+        <x:v>46194</x:v>
       </x:c>
       <x:c r="B163" s="16" t="str">
-        <x:v>Sumber Raya</x:v>
+        <x:v>Keraton</x:v>
       </x:c>
       <x:c r="C163" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D163" s="17" t="n">
-        <x:v>22</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E163" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F163" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="15" t="n">
-        <x:v>46193</x:v>
+        <x:v>46194</x:v>
       </x:c>
       <x:c r="B164" s="16" t="str">
-        <x:v>Beras Walet</x:v>
+        <x:v>Pandan Wangi</x:v>
       </x:c>
       <x:c r="C164" s="17" t="n">
-        <x:v>31</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D164" s="17" t="n">
         <x:v>0</x:v>
@@ -3564,13 +3565,13 @@
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="15" t="n">
-        <x:v>46193</x:v>
+        <x:v>46194</x:v>
       </x:c>
       <x:c r="B165" s="16" t="str">
-        <x:v>Cap Kembang</x:v>
+        <x:v>Ramos</x:v>
       </x:c>
       <x:c r="C165" s="17" t="n">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D165" s="17" t="n">
         <x:v>0</x:v>
@@ -3584,96 +3585,96 @@
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="15" t="n">
-        <x:v>46193</x:v>
+        <x:v>46194</x:v>
       </x:c>
       <x:c r="B166" s="16" t="str">
-        <x:v>Ir Cap Mercy</x:v>
+        <x:v>BMW</x:v>
       </x:c>
       <x:c r="C166" s="17" t="n">
-        <x:v>24</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D166" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E166" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F166" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="15" t="n">
-        <x:v>46193</x:v>
+        <x:v>46194</x:v>
       </x:c>
       <x:c r="B167" s="16" t="str">
-        <x:v>Karya Makmur</x:v>
+        <x:v>Beras Walet</x:v>
       </x:c>
       <x:c r="C167" s="17" t="n">
-        <x:v>30</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D167" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E167" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F167" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="15" t="n">
-        <x:v>46193</x:v>
+        <x:v>46194</x:v>
       </x:c>
       <x:c r="B168" s="16" t="str">
-        <x:v>Pandan Wangi</x:v>
+        <x:v>Cap Kembang</x:v>
       </x:c>
       <x:c r="C168" s="17" t="n">
-        <x:v>25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D168" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E168" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F168" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="169">
       <x:c r="A169" s="15" t="n">
-        <x:v>46193</x:v>
+        <x:v>46194</x:v>
       </x:c>
       <x:c r="B169" s="16" t="str">
-        <x:v>Ramos</x:v>
+        <x:v>Ir Cap Mercy</x:v>
       </x:c>
       <x:c r="C169" s="17" t="n">
-        <x:v>36</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D169" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E169" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F169" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="170">
       <x:c r="A170" s="15" t="n">
-        <x:v>46193</x:v>
+        <x:v>46194</x:v>
       </x:c>
       <x:c r="B170" s="16" t="str">
-        <x:v>BMW</x:v>
+        <x:v>Karya Makmur</x:v>
       </x:c>
       <x:c r="C170" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D170" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E170" s="16" t="str">
         <x:v>Karung</x:v>
@@ -3684,16 +3685,16 @@
     </x:row>
     <x:row r="171">
       <x:c r="A171" s="15" t="n">
-        <x:v>46193</x:v>
+        <x:v>46194</x:v>
       </x:c>
       <x:c r="B171" s="16" t="str">
-        <x:v>Cap Kembang</x:v>
+        <x:v>Rojo Lele</x:v>
       </x:c>
       <x:c r="C171" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D171" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E171" s="16" t="str">
         <x:v>Karung</x:v>
@@ -3704,16 +3705,16 @@
     </x:row>
     <x:row r="172">
       <x:c r="A172" s="15" t="n">
-        <x:v>46193</x:v>
+        <x:v>46195</x:v>
       </x:c>
       <x:c r="B172" s="16" t="str">
-        <x:v>Ir Cap Mercy</x:v>
+        <x:v>Beras Walet</x:v>
       </x:c>
       <x:c r="C172" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D172" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E172" s="16" t="str">
         <x:v>Karung</x:v>
@@ -3724,16 +3725,16 @@
     </x:row>
     <x:row r="173">
       <x:c r="A173" s="15" t="n">
-        <x:v>46193</x:v>
+        <x:v>46195</x:v>
       </x:c>
       <x:c r="B173" s="16" t="str">
-        <x:v>Keraton</x:v>
+        <x:v>Karya Makmur</x:v>
       </x:c>
       <x:c r="C173" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D173" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E173" s="16" t="str">
         <x:v>Karung</x:v>
@@ -3744,7 +3745,7 @@
     </x:row>
     <x:row r="174">
       <x:c r="A174" s="15" t="n">
-        <x:v>46193</x:v>
+        <x:v>46195</x:v>
       </x:c>
       <x:c r="B174" s="16" t="str">
         <x:v>Pandan Wangi</x:v>
@@ -3753,7 +3754,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D174" s="17" t="n">
-        <x:v>27</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E174" s="16" t="str">
         <x:v>Karung</x:v>
@@ -3764,7 +3765,7 @@
     </x:row>
     <x:row r="175">
       <x:c r="A175" s="15" t="n">
-        <x:v>46193</x:v>
+        <x:v>46195</x:v>
       </x:c>
       <x:c r="B175" s="16" t="str">
         <x:v>Ramos</x:v>
@@ -3773,7 +3774,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D175" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E175" s="16" t="str">
         <x:v>Karung</x:v>
@@ -3784,7 +3785,7 @@
     </x:row>
     <x:row r="176">
       <x:c r="A176" s="15" t="n">
-        <x:v>46193</x:v>
+        <x:v>46195</x:v>
       </x:c>
       <x:c r="B176" s="16" t="str">
         <x:v>Rojo Lele</x:v>
@@ -3793,7 +3794,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D176" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E176" s="16" t="str">
         <x:v>Karung</x:v>
@@ -3804,16 +3805,16 @@
     </x:row>
     <x:row r="177">
       <x:c r="A177" s="15" t="n">
-        <x:v>46194</x:v>
+        <x:v>46195</x:v>
       </x:c>
       <x:c r="B177" s="16" t="str">
-        <x:v>BMW</x:v>
+        <x:v>Sumber Raya</x:v>
       </x:c>
       <x:c r="C177" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D177" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E177" s="16" t="str">
         <x:v>Karung</x:v>
@@ -3824,16 +3825,16 @@
     </x:row>
     <x:row r="178">
       <x:c r="A178" s="15" t="n">
-        <x:v>46194</x:v>
+        <x:v>46196</x:v>
       </x:c>
       <x:c r="B178" s="16" t="str">
-        <x:v>Ir Cap Mercy</x:v>
+        <x:v>BMW</x:v>
       </x:c>
       <x:c r="C178" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D178" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E178" s="16" t="str">
         <x:v>Karung</x:v>
@@ -3844,7 +3845,7 @@
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="15" t="n">
-        <x:v>46194</x:v>
+        <x:v>46196</x:v>
       </x:c>
       <x:c r="B179" s="16" t="str">
         <x:v>Karya Makmur</x:v>
@@ -3853,7 +3854,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D179" s="17" t="n">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E179" s="16" t="str">
         <x:v>Karung</x:v>
@@ -3864,7 +3865,7 @@
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="15" t="n">
-        <x:v>46194</x:v>
+        <x:v>46196</x:v>
       </x:c>
       <x:c r="B180" s="16" t="str">
         <x:v>Keraton</x:v>
@@ -3873,7 +3874,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D180" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E180" s="16" t="str">
         <x:v>Karung</x:v>
@@ -3884,7 +3885,7 @@
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="15" t="n">
-        <x:v>46194</x:v>
+        <x:v>46196</x:v>
       </x:c>
       <x:c r="B181" s="16" t="str">
         <x:v>Ramos</x:v>
@@ -3893,7 +3894,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D181" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E181" s="16" t="str">
         <x:v>Karung</x:v>
@@ -3904,53 +3905,53 @@
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="15" t="n">
-        <x:v>46195</x:v>
+        <x:v>46196</x:v>
       </x:c>
       <x:c r="B182" s="16" t="str">
-        <x:v>BMW</x:v>
+        <x:v>Rojo Lele</x:v>
       </x:c>
       <x:c r="C182" s="17" t="n">
-        <x:v>24</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D182" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E182" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F182" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="15" t="n">
-        <x:v>46195</x:v>
+        <x:v>46196</x:v>
       </x:c>
       <x:c r="B183" s="16" t="str">
-        <x:v>Cap Kembang</x:v>
+        <x:v>Sumber Raya</x:v>
       </x:c>
       <x:c r="C183" s="17" t="n">
-        <x:v>28</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D183" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E183" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F183" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="15" t="n">
-        <x:v>46195</x:v>
+        <x:v>46197</x:v>
       </x:c>
       <x:c r="B184" s="16" t="str">
-        <x:v>Ir Cap Mercy</x:v>
+        <x:v>BMW</x:v>
       </x:c>
       <x:c r="C184" s="17" t="n">
-        <x:v>34</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D184" s="17" t="n">
         <x:v>0</x:v>
@@ -3964,13 +3965,13 @@
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="15" t="n">
-        <x:v>46195</x:v>
+        <x:v>46197</x:v>
       </x:c>
       <x:c r="B185" s="16" t="str">
-        <x:v>Keraton</x:v>
+        <x:v>Beras Walet</x:v>
       </x:c>
       <x:c r="C185" s="17" t="n">
-        <x:v>37</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D185" s="17" t="n">
         <x:v>0</x:v>
@@ -3984,13 +3985,13 @@
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="15" t="n">
-        <x:v>46195</x:v>
+        <x:v>46197</x:v>
       </x:c>
       <x:c r="B186" s="16" t="str">
-        <x:v>Pandan Wangi</x:v>
+        <x:v>Cap Kembang</x:v>
       </x:c>
       <x:c r="C186" s="17" t="n">
-        <x:v>30</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D186" s="17" t="n">
         <x:v>0</x:v>
@@ -4004,13 +4005,13 @@
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="15" t="n">
-        <x:v>46195</x:v>
+        <x:v>46197</x:v>
       </x:c>
       <x:c r="B187" s="16" t="str">
-        <x:v>Ramos</x:v>
+        <x:v>Pandan Wangi</x:v>
       </x:c>
       <x:c r="C187" s="17" t="n">
-        <x:v>22</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D187" s="17" t="n">
         <x:v>0</x:v>
@@ -4024,13 +4025,13 @@
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="15" t="n">
-        <x:v>46195</x:v>
+        <x:v>46197</x:v>
       </x:c>
       <x:c r="B188" s="16" t="str">
         <x:v>Rojo Lele</x:v>
       </x:c>
       <x:c r="C188" s="17" t="n">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D188" s="17" t="n">
         <x:v>0</x:v>
@@ -4044,36 +4045,36 @@
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="15" t="n">
-        <x:v>46195</x:v>
+        <x:v>46197</x:v>
       </x:c>
       <x:c r="B189" s="16" t="str">
-        <x:v>BMW</x:v>
+        <x:v>Sumber Raya</x:v>
       </x:c>
       <x:c r="C189" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D189" s="17" t="n">
-        <x:v>14</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E189" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F189" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="15" t="n">
-        <x:v>46195</x:v>
+        <x:v>46197</x:v>
       </x:c>
       <x:c r="B190" s="16" t="str">
-        <x:v>Ir Cap Mercy</x:v>
+        <x:v>BMW</x:v>
       </x:c>
       <x:c r="C190" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D190" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E190" s="16" t="str">
         <x:v>Karung</x:v>
@@ -4084,7 +4085,7 @@
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="15" t="n">
-        <x:v>46195</x:v>
+        <x:v>46197</x:v>
       </x:c>
       <x:c r="B191" s="16" t="str">
         <x:v>Karya Makmur</x:v>
@@ -4093,7 +4094,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D191" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E191" s="16" t="str">
         <x:v>Karung</x:v>
@@ -4104,16 +4105,16 @@
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="15" t="n">
-        <x:v>46195</x:v>
+        <x:v>46197</x:v>
       </x:c>
       <x:c r="B192" s="16" t="str">
-        <x:v>Keraton</x:v>
+        <x:v>Pandan Wangi</x:v>
       </x:c>
       <x:c r="C192" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D192" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E192" s="16" t="str">
         <x:v>Karung</x:v>
@@ -4124,16 +4125,16 @@
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="15" t="n">
-        <x:v>46195</x:v>
+        <x:v>46197</x:v>
       </x:c>
       <x:c r="B193" s="16" t="str">
-        <x:v>Pandan Wangi</x:v>
+        <x:v>Ramos</x:v>
       </x:c>
       <x:c r="C193" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D193" s="17" t="n">
-        <x:v>22</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E193" s="16" t="str">
         <x:v>Karung</x:v>
@@ -4144,7 +4145,7 @@
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="15" t="n">
-        <x:v>46195</x:v>
+        <x:v>46197</x:v>
       </x:c>
       <x:c r="B194" s="16" t="str">
         <x:v>Sumber Raya</x:v>
@@ -4153,7 +4154,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D194" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E194" s="16" t="str">
         <x:v>Karung</x:v>
@@ -4164,16 +4165,16 @@
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="15" t="n">
-        <x:v>46196</x:v>
+        <x:v>46198</x:v>
       </x:c>
       <x:c r="B195" s="16" t="str">
-        <x:v>Cap Kembang</x:v>
+        <x:v>BMW</x:v>
       </x:c>
       <x:c r="C195" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D195" s="17" t="n">
-        <x:v>17</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E195" s="16" t="str">
         <x:v>Karung</x:v>
@@ -4184,7 +4185,7 @@
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="15" t="n">
-        <x:v>46196</x:v>
+        <x:v>46198</x:v>
       </x:c>
       <x:c r="B196" s="16" t="str">
         <x:v>Ir Cap Mercy</x:v>
@@ -4193,7 +4194,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D196" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E196" s="16" t="str">
         <x:v>Karung</x:v>
@@ -4204,16 +4205,16 @@
     </x:row>
     <x:row r="197">
       <x:c r="A197" s="15" t="n">
-        <x:v>46196</x:v>
+        <x:v>46198</x:v>
       </x:c>
       <x:c r="B197" s="16" t="str">
-        <x:v>Karya Makmur</x:v>
+        <x:v>Keraton</x:v>
       </x:c>
       <x:c r="C197" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D197" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E197" s="16" t="str">
         <x:v>Karung</x:v>
@@ -4224,7 +4225,7 @@
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="15" t="n">
-        <x:v>46196</x:v>
+        <x:v>46198</x:v>
       </x:c>
       <x:c r="B198" s="16" t="str">
         <x:v>Pandan Wangi</x:v>
@@ -4233,7 +4234,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D198" s="17" t="n">
-        <x:v>28</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E198" s="16" t="str">
         <x:v>Karung</x:v>
@@ -4244,7 +4245,7 @@
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="15" t="n">
-        <x:v>46196</x:v>
+        <x:v>46198</x:v>
       </x:c>
       <x:c r="B199" s="16" t="str">
         <x:v>Ramos</x:v>
@@ -4253,7 +4254,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D199" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E199" s="16" t="str">
         <x:v>Karung</x:v>
@@ -4264,16 +4265,16 @@
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="15" t="n">
-        <x:v>46196</x:v>
+        <x:v>46198</x:v>
       </x:c>
       <x:c r="B200" s="16" t="str">
-        <x:v>Rojo Lele</x:v>
+        <x:v>Sumber Raya</x:v>
       </x:c>
       <x:c r="C200" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D200" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E200" s="16" t="str">
         <x:v>Karung</x:v>
@@ -4284,33 +4285,33 @@
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="15" t="n">
-        <x:v>46196</x:v>
+        <x:v>46199</x:v>
       </x:c>
       <x:c r="B201" s="16" t="str">
-        <x:v>Sumber Raya</x:v>
+        <x:v>BMW</x:v>
       </x:c>
       <x:c r="C201" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D201" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E201" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F201" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="202">
       <x:c r="A202" s="15" t="n">
-        <x:v>46197</x:v>
+        <x:v>46199</x:v>
       </x:c>
       <x:c r="B202" s="16" t="str">
-        <x:v>Cap Kembang</x:v>
+        <x:v>Karya Makmur</x:v>
       </x:c>
       <x:c r="C202" s="17" t="n">
-        <x:v>32</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D202" s="17" t="n">
         <x:v>0</x:v>
@@ -4324,13 +4325,13 @@
     </x:row>
     <x:row r="203">
       <x:c r="A203" s="15" t="n">
-        <x:v>46197</x:v>
+        <x:v>46199</x:v>
       </x:c>
       <x:c r="B203" s="16" t="str">
-        <x:v>Ir Cap Mercy</x:v>
+        <x:v>Keraton</x:v>
       </x:c>
       <x:c r="C203" s="17" t="n">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D203" s="17" t="n">
         <x:v>0</x:v>
@@ -4344,13 +4345,13 @@
     </x:row>
     <x:row r="204">
       <x:c r="A204" s="15" t="n">
-        <x:v>46197</x:v>
+        <x:v>46199</x:v>
       </x:c>
       <x:c r="B204" s="16" t="str">
-        <x:v>Karya Makmur</x:v>
+        <x:v>Pandan Wangi</x:v>
       </x:c>
       <x:c r="C204" s="17" t="n">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D204" s="17" t="n">
         <x:v>0</x:v>
@@ -4364,13 +4365,13 @@
     </x:row>
     <x:row r="205">
       <x:c r="A205" s="15" t="n">
-        <x:v>46197</x:v>
+        <x:v>46199</x:v>
       </x:c>
       <x:c r="B205" s="16" t="str">
         <x:v>Pandan Wangi</x:v>
       </x:c>
       <x:c r="C205" s="17" t="n">
-        <x:v>27</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D205" s="17" t="n">
         <x:v>0</x:v>
@@ -4379,18 +4380,18 @@
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F205" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Tambahan stok masuk sesuai kebutuhan gudang, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="206">
       <x:c r="A206" s="15" t="n">
-        <x:v>46197</x:v>
+        <x:v>46199</x:v>
       </x:c>
       <x:c r="B206" s="16" t="str">
         <x:v>Ramos</x:v>
       </x:c>
       <x:c r="C206" s="17" t="n">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D206" s="17" t="n">
         <x:v>0</x:v>
@@ -4404,36 +4405,36 @@
     </x:row>
     <x:row r="207">
       <x:c r="A207" s="15" t="n">
-        <x:v>46197</x:v>
+        <x:v>46199</x:v>
       </x:c>
       <x:c r="B207" s="16" t="str">
-        <x:v>Sumber Raya</x:v>
+        <x:v>BMW</x:v>
       </x:c>
       <x:c r="C207" s="17" t="n">
-        <x:v>24</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D207" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E207" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F207" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="208">
       <x:c r="A208" s="15" t="n">
-        <x:v>46197</x:v>
+        <x:v>46199</x:v>
       </x:c>
       <x:c r="B208" s="16" t="str">
-        <x:v>BMW</x:v>
+        <x:v>Cap Kembang</x:v>
       </x:c>
       <x:c r="C208" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D208" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E208" s="16" t="str">
         <x:v>Karung</x:v>
@@ -4444,16 +4445,16 @@
     </x:row>
     <x:row r="209">
       <x:c r="A209" s="15" t="n">
-        <x:v>46197</x:v>
+        <x:v>46199</x:v>
       </x:c>
       <x:c r="B209" s="16" t="str">
-        <x:v>Beras Walet</x:v>
+        <x:v>Ir Cap Mercy</x:v>
       </x:c>
       <x:c r="C209" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D209" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E209" s="16" t="str">
         <x:v>Karung</x:v>
@@ -4464,16 +4465,16 @@
     </x:row>
     <x:row r="210">
       <x:c r="A210" s="15" t="n">
-        <x:v>46197</x:v>
+        <x:v>46199</x:v>
       </x:c>
       <x:c r="B210" s="16" t="str">
-        <x:v>Cap Kembang</x:v>
+        <x:v>Karya Makmur</x:v>
       </x:c>
       <x:c r="C210" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D210" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E210" s="16" t="str">
         <x:v>Karung</x:v>
@@ -4484,16 +4485,16 @@
     </x:row>
     <x:row r="211">
       <x:c r="A211" s="15" t="n">
-        <x:v>46197</x:v>
+        <x:v>46199</x:v>
       </x:c>
       <x:c r="B211" s="16" t="str">
-        <x:v>Ir Cap Mercy</x:v>
+        <x:v>Pandan Wangi</x:v>
       </x:c>
       <x:c r="C211" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D211" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E211" s="16" t="str">
         <x:v>Karung</x:v>
@@ -4504,16 +4505,16 @@
     </x:row>
     <x:row r="212">
       <x:c r="A212" s="15" t="n">
-        <x:v>46197</x:v>
+        <x:v>46199</x:v>
       </x:c>
       <x:c r="B212" s="16" t="str">
-        <x:v>Karya Makmur</x:v>
+        <x:v>Ramos</x:v>
       </x:c>
       <x:c r="C212" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D212" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E212" s="16" t="str">
         <x:v>Karung</x:v>
@@ -4524,16 +4525,16 @@
     </x:row>
     <x:row r="213">
       <x:c r="A213" s="15" t="n">
-        <x:v>46197</x:v>
+        <x:v>46199</x:v>
       </x:c>
       <x:c r="B213" s="16" t="str">
-        <x:v>Keraton</x:v>
+        <x:v>Rojo Lele</x:v>
       </x:c>
       <x:c r="C213" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D213" s="17" t="n">
-        <x:v>23</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E213" s="16" t="str">
         <x:v>Karung</x:v>
@@ -4544,16 +4545,16 @@
     </x:row>
     <x:row r="214">
       <x:c r="A214" s="15" t="n">
-        <x:v>46197</x:v>
+        <x:v>46199</x:v>
       </x:c>
       <x:c r="B214" s="16" t="str">
-        <x:v>Pandan Wangi</x:v>
+        <x:v>Sumber Raya</x:v>
       </x:c>
       <x:c r="C214" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D214" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E214" s="16" t="str">
         <x:v>Karung</x:v>
@@ -4564,16 +4565,16 @@
     </x:row>
     <x:row r="215">
       <x:c r="A215" s="15" t="n">
-        <x:v>46197</x:v>
+        <x:v>46200</x:v>
       </x:c>
       <x:c r="B215" s="16" t="str">
-        <x:v>Rojo Lele</x:v>
+        <x:v>Cap Kembang</x:v>
       </x:c>
       <x:c r="C215" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D215" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E215" s="16" t="str">
         <x:v>Karung</x:v>
@@ -4584,16 +4585,16 @@
     </x:row>
     <x:row r="216">
       <x:c r="A216" s="15" t="n">
-        <x:v>46198</x:v>
+        <x:v>46200</x:v>
       </x:c>
       <x:c r="B216" s="16" t="str">
-        <x:v>BMW</x:v>
+        <x:v>Ir Cap Mercy</x:v>
       </x:c>
       <x:c r="C216" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D216" s="17" t="n">
-        <x:v>34</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E216" s="16" t="str">
         <x:v>Karung</x:v>
@@ -4604,16 +4605,16 @@
     </x:row>
     <x:row r="217">
       <x:c r="A217" s="15" t="n">
-        <x:v>46198</x:v>
+        <x:v>46200</x:v>
       </x:c>
       <x:c r="B217" s="16" t="str">
-        <x:v>Beras Walet</x:v>
+        <x:v>Keraton</x:v>
       </x:c>
       <x:c r="C217" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D217" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E217" s="16" t="str">
         <x:v>Karung</x:v>
@@ -4624,16 +4625,16 @@
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="15" t="n">
-        <x:v>46198</x:v>
+        <x:v>46200</x:v>
       </x:c>
       <x:c r="B218" s="16" t="str">
-        <x:v>Cap Kembang</x:v>
+        <x:v>Pandan Wangi</x:v>
       </x:c>
       <x:c r="C218" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D218" s="17" t="n">
-        <x:v>15</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E218" s="16" t="str">
         <x:v>Karung</x:v>
@@ -4644,16 +4645,16 @@
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="15" t="n">
-        <x:v>46198</x:v>
+        <x:v>46200</x:v>
       </x:c>
       <x:c r="B219" s="16" t="str">
-        <x:v>Ir Cap Mercy</x:v>
+        <x:v>Ramos</x:v>
       </x:c>
       <x:c r="C219" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D219" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E219" s="16" t="str">
         <x:v>Karung</x:v>
@@ -4664,16 +4665,16 @@
     </x:row>
     <x:row r="220">
       <x:c r="A220" s="15" t="n">
-        <x:v>46198</x:v>
+        <x:v>46200</x:v>
       </x:c>
       <x:c r="B220" s="16" t="str">
-        <x:v>Keraton</x:v>
+        <x:v>Rojo Lele</x:v>
       </x:c>
       <x:c r="C220" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D220" s="17" t="n">
-        <x:v>30</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E220" s="16" t="str">
         <x:v>Karung</x:v>
@@ -4684,16 +4685,16 @@
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="15" t="n">
-        <x:v>46199</x:v>
+        <x:v>46200</x:v>
       </x:c>
       <x:c r="B221" s="16" t="str">
-        <x:v>Beras Walet</x:v>
+        <x:v>Sumber Raya</x:v>
       </x:c>
       <x:c r="C221" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D221" s="17" t="n">
-        <x:v>21</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E221" s="16" t="str">
         <x:v>Karung</x:v>
@@ -4704,53 +4705,53 @@
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="15" t="n">
-        <x:v>46199</x:v>
+        <x:v>46201</x:v>
       </x:c>
       <x:c r="B222" s="16" t="str">
-        <x:v>Ramos</x:v>
+        <x:v>Beras Walet</x:v>
       </x:c>
       <x:c r="C222" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D222" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E222" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F222" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="223">
       <x:c r="A223" s="15" t="n">
-        <x:v>46199</x:v>
+        <x:v>46201</x:v>
       </x:c>
       <x:c r="B223" s="16" t="str">
-        <x:v>Sumber Raya</x:v>
+        <x:v>Cap Kembang</x:v>
       </x:c>
       <x:c r="C223" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D223" s="17" t="n">
-        <x:v>41</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E223" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F223" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
+        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
       </x:c>
     </x:row>
     <x:row r="224">
       <x:c r="A224" s="15" t="n">
-        <x:v>46200</x:v>
+        <x:v>46201</x:v>
       </x:c>
       <x:c r="B224" s="16" t="str">
-        <x:v>BMW</x:v>
+        <x:v>Ir Cap Mercy</x:v>
       </x:c>
       <x:c r="C224" s="17" t="n">
-        <x:v>32</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D224" s="17" t="n">
         <x:v>0</x:v>
@@ -4764,13 +4765,13 @@
     </x:row>
     <x:row r="225">
       <x:c r="A225" s="15" t="n">
-        <x:v>46200</x:v>
+        <x:v>46201</x:v>
       </x:c>
       <x:c r="B225" s="16" t="str">
-        <x:v>Beras Walet</x:v>
+        <x:v>Karya Makmur</x:v>
       </x:c>
       <x:c r="C225" s="17" t="n">
-        <x:v>36</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D225" s="17" t="n">
         <x:v>0</x:v>
@@ -4784,13 +4785,13 @@
     </x:row>
     <x:row r="226">
       <x:c r="A226" s="15" t="n">
-        <x:v>46200</x:v>
+        <x:v>46201</x:v>
       </x:c>
       <x:c r="B226" s="16" t="str">
-        <x:v>Keraton</x:v>
+        <x:v>Ramos</x:v>
       </x:c>
       <x:c r="C226" s="17" t="n">
-        <x:v>24</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D226" s="17" t="n">
         <x:v>0</x:v>
@@ -4804,13 +4805,13 @@
     </x:row>
     <x:row r="227">
       <x:c r="A227" s="15" t="n">
-        <x:v>46200</x:v>
+        <x:v>46201</x:v>
       </x:c>
       <x:c r="B227" s="16" t="str">
-        <x:v>Pandan Wangi</x:v>
+        <x:v>Sumber Raya</x:v>
       </x:c>
       <x:c r="C227" s="17" t="n">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D227" s="17" t="n">
         <x:v>0</x:v>
@@ -4824,56 +4825,56 @@
     </x:row>
     <x:row r="228">
       <x:c r="A228" s="15" t="n">
-        <x:v>46200</x:v>
+        <x:v>46201</x:v>
       </x:c>
       <x:c r="B228" s="16" t="str">
-        <x:v>Sumber Raya</x:v>
+        <x:v>BMW</x:v>
       </x:c>
       <x:c r="C228" s="17" t="n">
-        <x:v>29</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D228" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E228" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F228" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="229">
       <x:c r="A229" s="15" t="n">
-        <x:v>46200</x:v>
+        <x:v>46201</x:v>
       </x:c>
       <x:c r="B229" s="16" t="str">
-        <x:v>Sumber Raya</x:v>
+        <x:v>Cap Kembang</x:v>
       </x:c>
       <x:c r="C229" s="17" t="n">
-        <x:v>33</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D229" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E229" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F229" s="16" t="str">
-        <x:v>Tambahan stok masuk sesuai kebutuhan gudang, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="230">
       <x:c r="A230" s="15" t="n">
-        <x:v>46200</x:v>
+        <x:v>46201</x:v>
       </x:c>
       <x:c r="B230" s="16" t="str">
-        <x:v>Beras Walet</x:v>
+        <x:v>Karya Makmur</x:v>
       </x:c>
       <x:c r="C230" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D230" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E230" s="16" t="str">
         <x:v>Karung</x:v>
@@ -4884,7 +4885,7 @@
     </x:row>
     <x:row r="231">
       <x:c r="A231" s="15" t="n">
-        <x:v>46200</x:v>
+        <x:v>46201</x:v>
       </x:c>
       <x:c r="B231" s="16" t="str">
         <x:v>Keraton</x:v>
@@ -4893,7 +4894,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D231" s="17" t="n">
-        <x:v>21</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E231" s="16" t="str">
         <x:v>Karung</x:v>
@@ -4904,16 +4905,16 @@
     </x:row>
     <x:row r="232">
       <x:c r="A232" s="15" t="n">
-        <x:v>46200</x:v>
+        <x:v>46201</x:v>
       </x:c>
       <x:c r="B232" s="16" t="str">
-        <x:v>Pandan Wangi</x:v>
+        <x:v>Ramos</x:v>
       </x:c>
       <x:c r="C232" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D232" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E232" s="16" t="str">
         <x:v>Karung</x:v>
@@ -4924,16 +4925,16 @@
     </x:row>
     <x:row r="233">
       <x:c r="A233" s="15" t="n">
-        <x:v>46200</x:v>
+        <x:v>46201</x:v>
       </x:c>
       <x:c r="B233" s="16" t="str">
-        <x:v>Ramos</x:v>
+        <x:v>Sumber Raya</x:v>
       </x:c>
       <x:c r="C233" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D233" s="17" t="n">
-        <x:v>5</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E233" s="16" t="str">
         <x:v>Karung</x:v>
@@ -4944,16 +4945,16 @@
     </x:row>
     <x:row r="234">
       <x:c r="A234" s="15" t="n">
-        <x:v>46200</x:v>
+        <x:v>46202</x:v>
       </x:c>
       <x:c r="B234" s="16" t="str">
-        <x:v>Rojo Lele</x:v>
+        <x:v>BMW</x:v>
       </x:c>
       <x:c r="C234" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D234" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E234" s="16" t="str">
         <x:v>Karung</x:v>
@@ -4964,16 +4965,16 @@
     </x:row>
     <x:row r="235">
       <x:c r="A235" s="15" t="n">
-        <x:v>46201</x:v>
+        <x:v>46202</x:v>
       </x:c>
       <x:c r="B235" s="16" t="str">
-        <x:v>BMW</x:v>
+        <x:v>Beras Walet</x:v>
       </x:c>
       <x:c r="C235" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D235" s="17" t="n">
-        <x:v>12</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E235" s="16" t="str">
         <x:v>Karung</x:v>
@@ -4984,16 +4985,16 @@
     </x:row>
     <x:row r="236">
       <x:c r="A236" s="15" t="n">
-        <x:v>46201</x:v>
+        <x:v>46202</x:v>
       </x:c>
       <x:c r="B236" s="16" t="str">
-        <x:v>Beras Walet</x:v>
+        <x:v>Ir Cap Mercy</x:v>
       </x:c>
       <x:c r="C236" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D236" s="17" t="n">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E236" s="16" t="str">
         <x:v>Karung</x:v>
@@ -5004,16 +5005,16 @@
     </x:row>
     <x:row r="237">
       <x:c r="A237" s="15" t="n">
-        <x:v>46201</x:v>
+        <x:v>46202</x:v>
       </x:c>
       <x:c r="B237" s="16" t="str">
-        <x:v>Keraton</x:v>
+        <x:v>Karya Makmur</x:v>
       </x:c>
       <x:c r="C237" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D237" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E237" s="16" t="str">
         <x:v>Karung</x:v>
@@ -5024,16 +5025,16 @@
     </x:row>
     <x:row r="238">
       <x:c r="A238" s="15" t="n">
-        <x:v>46201</x:v>
+        <x:v>46202</x:v>
       </x:c>
       <x:c r="B238" s="16" t="str">
-        <x:v>Rojo Lele</x:v>
+        <x:v>Keraton</x:v>
       </x:c>
       <x:c r="C238" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D238" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E238" s="16" t="str">
         <x:v>Karung</x:v>
@@ -5047,19 +5048,19 @@
         <x:v>46202</x:v>
       </x:c>
       <x:c r="B239" s="16" t="str">
-        <x:v>BMW</x:v>
+        <x:v>Pandan Wangi</x:v>
       </x:c>
       <x:c r="C239" s="17" t="n">
-        <x:v>30</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D239" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E239" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F239" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="240">
@@ -5067,19 +5068,19 @@
         <x:v>46202</x:v>
       </x:c>
       <x:c r="B240" s="16" t="str">
-        <x:v>Beras Walet</x:v>
+        <x:v>Rojo Lele</x:v>
       </x:c>
       <x:c r="C240" s="17" t="n">
-        <x:v>26</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D240" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E240" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F240" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="241">
@@ -5087,87 +5088,87 @@
         <x:v>46202</x:v>
       </x:c>
       <x:c r="B241" s="16" t="str">
-        <x:v>Karya Makmur</x:v>
+        <x:v>Sumber Raya</x:v>
       </x:c>
       <x:c r="C241" s="17" t="n">
-        <x:v>29</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D241" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E241" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F241" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="242">
       <x:c r="A242" s="15" t="n">
-        <x:v>46202</x:v>
+        <x:v>46203</x:v>
       </x:c>
       <x:c r="B242" s="16" t="str">
-        <x:v>Keraton</x:v>
+        <x:v>Beras Walet</x:v>
       </x:c>
       <x:c r="C242" s="17" t="n">
-        <x:v>25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D242" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E242" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F242" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="243">
       <x:c r="A243" s="15" t="n">
-        <x:v>46202</x:v>
+        <x:v>46203</x:v>
       </x:c>
       <x:c r="B243" s="16" t="str">
-        <x:v>Pandan Wangi</x:v>
+        <x:v>Ir Cap Mercy</x:v>
       </x:c>
       <x:c r="C243" s="17" t="n">
-        <x:v>37</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D243" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E243" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F243" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="244">
       <x:c r="A244" s="15" t="n">
-        <x:v>46202</x:v>
+        <x:v>46203</x:v>
       </x:c>
       <x:c r="B244" s="16" t="str">
-        <x:v>Rojo Lele</x:v>
+        <x:v>Pandan Wangi</x:v>
       </x:c>
       <x:c r="C244" s="17" t="n">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D244" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E244" s="16" t="str">
         <x:v>Karung</x:v>
       </x:c>
       <x:c r="F244" s="16" t="str">
-        <x:v>Stok masuk rutin 3x seminggu, asumsi 1 karung = 50 kg.</x:v>
+        <x:v>Penjualan/pengeluaran stok harian.</x:v>
       </x:c>
     </x:row>
     <x:row r="245">
       <x:c r="A245" s="15" t="n">
-        <x:v>46202</x:v>
+        <x:v>46203</x:v>
       </x:c>
       <x:c r="B245" s="16" t="str">
-        <x:v>BMW</x:v>
+        <x:v>Ramos</x:v>
       </x:c>
       <x:c r="C245" s="17" t="n">
         <x:v>0</x:v>
@@ -5184,16 +5185,16 @@
     </x:row>
     <x:row r="246">
       <x:c r="A246" s="15" t="n">
-        <x:v>46202</x:v>
+        <x:v>46203</x:v>
       </x:c>
       <x:c r="B246" s="16" t="str">
-        <x:v>Beras Walet</x:v>
+        <x:v>Sumber Raya</x:v>
       </x:c>
       <x:c r="C246" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D246" s="17" t="n">
-        <x:v>27</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E246" s="16" t="str">
         <x:v>Karung</x:v>
@@ -5203,189 +5204,105 @@
       </x:c>
     </x:row>
     <x:row r="247">
-      <x:c r="A247" s="15" t="n">
-        <x:v>46202</x:v>
-      </x:c>
-      <x:c r="B247" s="16" t="str">
-        <x:v>Karya Makmur</x:v>
-      </x:c>
-      <x:c r="C247" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D247" s="17" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="E247" s="16" t="str">
-        <x:v>Karung</x:v>
-      </x:c>
-      <x:c r="F247" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
-      </x:c>
+      <x:c r="A247" s="15"/>
+      <x:c r="B247" s="16"/>
+      <x:c r="C247" s="17"/>
+      <x:c r="D247" s="17"/>
+      <x:c r="E247" s="16"/>
+      <x:c r="F247" s="16"/>
     </x:row>
     <x:row r="248">
-      <x:c r="A248" s="15" t="n">
-        <x:v>46202</x:v>
-      </x:c>
-      <x:c r="B248" s="16" t="str">
-        <x:v>Keraton</x:v>
-      </x:c>
-      <x:c r="C248" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D248" s="17" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E248" s="16" t="str">
-        <x:v>Karung</x:v>
-      </x:c>
-      <x:c r="F248" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
-      </x:c>
+      <x:c r="A248" s="15"/>
+      <x:c r="B248" s="16"/>
+      <x:c r="C248" s="17"/>
+      <x:c r="D248" s="17"/>
+      <x:c r="E248" s="16"/>
+      <x:c r="F248" s="16"/>
     </x:row>
     <x:row r="249">
-      <x:c r="A249" s="15" t="n">
-        <x:v>46202</x:v>
-      </x:c>
-      <x:c r="B249" s="16" t="str">
-        <x:v>Pandan Wangi</x:v>
-      </x:c>
-      <x:c r="C249" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D249" s="17" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E249" s="16" t="str">
-        <x:v>Karung</x:v>
-      </x:c>
-      <x:c r="F249" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
-      </x:c>
+      <x:c r="A249" s="15"/>
+      <x:c r="B249" s="16"/>
+      <x:c r="C249" s="17"/>
+      <x:c r="D249" s="17"/>
+      <x:c r="E249" s="16"/>
+      <x:c r="F249" s="16"/>
     </x:row>
     <x:row r="250">
-      <x:c r="A250" s="15" t="n">
-        <x:v>46202</x:v>
-      </x:c>
-      <x:c r="B250" s="16" t="str">
-        <x:v>Ramos</x:v>
-      </x:c>
-      <x:c r="C250" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D250" s="17" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E250" s="16" t="str">
-        <x:v>Karung</x:v>
-      </x:c>
-      <x:c r="F250" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
-      </x:c>
+      <x:c r="A250" s="15"/>
+      <x:c r="B250" s="16"/>
+      <x:c r="C250" s="17"/>
+      <x:c r="D250" s="17"/>
+      <x:c r="E250" s="16"/>
+      <x:c r="F250" s="16"/>
     </x:row>
     <x:row r="251">
-      <x:c r="A251" s="15" t="n">
-        <x:v>46203</x:v>
-      </x:c>
-      <x:c r="B251" s="16" t="str">
-        <x:v>BMW</x:v>
-      </x:c>
-      <x:c r="C251" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D251" s="17" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E251" s="16" t="str">
-        <x:v>Karung</x:v>
-      </x:c>
-      <x:c r="F251" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
-      </x:c>
+      <x:c r="A251" s="15"/>
+      <x:c r="B251" s="16"/>
+      <x:c r="C251" s="17"/>
+      <x:c r="D251" s="17"/>
+      <x:c r="E251" s="16"/>
+      <x:c r="F251" s="16"/>
     </x:row>
     <x:row r="252">
-      <x:c r="A252" s="15" t="n">
-        <x:v>46203</x:v>
-      </x:c>
-      <x:c r="B252" s="16" t="str">
-        <x:v>Cap Kembang</x:v>
-      </x:c>
-      <x:c r="C252" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D252" s="17" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E252" s="16" t="str">
-        <x:v>Karung</x:v>
-      </x:c>
-      <x:c r="F252" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
-      </x:c>
+      <x:c r="A252" s="15"/>
+      <x:c r="B252" s="16"/>
+      <x:c r="C252" s="17"/>
+      <x:c r="D252" s="17"/>
+      <x:c r="E252" s="16"/>
+      <x:c r="F252" s="16"/>
     </x:row>
     <x:row r="253">
-      <x:c r="A253" s="15" t="n">
-        <x:v>46203</x:v>
-      </x:c>
-      <x:c r="B253" s="16" t="str">
-        <x:v>Karya Makmur</x:v>
-      </x:c>
-      <x:c r="C253" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D253" s="17" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E253" s="16" t="str">
-        <x:v>Karung</x:v>
-      </x:c>
-      <x:c r="F253" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
-      </x:c>
+      <x:c r="A253" s="15"/>
+      <x:c r="B253" s="16"/>
+      <x:c r="C253" s="17"/>
+      <x:c r="D253" s="17"/>
+      <x:c r="E253" s="16"/>
+      <x:c r="F253" s="16"/>
     </x:row>
     <x:row r="254">
-      <x:c r="A254" s="15" t="n">
-        <x:v>46203</x:v>
-      </x:c>
-      <x:c r="B254" s="16" t="str">
-        <x:v>Pandan Wangi</x:v>
-      </x:c>
-      <x:c r="C254" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D254" s="17" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="E254" s="16" t="str">
-        <x:v>Karung</x:v>
-      </x:c>
-      <x:c r="F254" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
-      </x:c>
+      <x:c r="A254" s="15"/>
+      <x:c r="B254" s="16"/>
+      <x:c r="C254" s="17"/>
+      <x:c r="D254" s="17"/>
+      <x:c r="E254" s="16"/>
+      <x:c r="F254" s="16"/>
     </x:row>
     <x:row r="255">
-      <x:c r="A255" s="15" t="n">
-        <x:v>46203</x:v>
-      </x:c>
-      <x:c r="B255" s="16" t="str">
-        <x:v>Rojo Lele</x:v>
-      </x:c>
-      <x:c r="C255" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D255" s="17" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E255" s="16" t="str">
-        <x:v>Karung</x:v>
-      </x:c>
-      <x:c r="F255" s="16" t="str">
-        <x:v>Penjualan/pengeluaran stok harian.</x:v>
-      </x:c>
+      <x:c r="A255" s="15"/>
+      <x:c r="B255" s="16"/>
+      <x:c r="C255" s="17"/>
+      <x:c r="D255" s="17"/>
+      <x:c r="E255" s="16"/>
+      <x:c r="F255" s="16"/>
+    </x:row>
+    <x:row r="256">
+      <x:c r="A256" s="15"/>
+      <x:c r="B256" s="16"/>
+      <x:c r="C256" s="17"/>
+      <x:c r="D256" s="17"/>
+      <x:c r="E256" s="16"/>
+      <x:c r="F256" s="16"/>
+    </x:row>
+    <x:row r="257">
+      <x:c r="A257" s="15"/>
+      <x:c r="B257" s="16"/>
+      <x:c r="C257" s="17"/>
+      <x:c r="D257" s="17"/>
+      <x:c r="E257" s="16"/>
+      <x:c r="F257" s="16"/>
+    </x:row>
+    <x:row r="258">
+      <x:c r="A258" s="15"/>
+      <x:c r="B258" s="16"/>
+      <x:c r="C258" s="17"/>
+      <x:c r="D258" s="17"/>
+      <x:c r="E258" s="16"/>
+      <x:c r="F258" s="16"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b09cd72478a4447"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde414281e06b429d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5403,7 +5320,7 @@
         <x:v>Ringkasan Data Stok</x:v>
       </x:c>
       <x:c r="B1" s="3" t="str">
-        <x:v>06 Juni</x:v>
+        <x:v>Juni 2026</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -5411,7 +5328,7 @@
         <x:v>Periode</x:v>
       </x:c>
       <x:c r="B2" s="16" t="str">
-        <x:v>06 Juni</x:v>
+        <x:v>01-30 Juni 2026</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -5419,7 +5336,7 @@
         <x:v>Jumlah baris valid</x:v>
       </x:c>
       <x:c r="B3" s="16" t="n">
-        <x:v>254</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -5427,7 +5344,7 @@
         <x:v>Total stok masuk (karung)</x:v>
       </x:c>
       <x:c r="B4" s="16" t="n">
-        <x:v>2319</x:v>
+        <x:v>2340</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -5435,7 +5352,7 @@
         <x:v>Total stok keluar (karung)</x:v>
       </x:c>
       <x:c r="B5" s="16" t="n">
-        <x:v>2262</x:v>
+        <x:v>2179</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
